--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_22_34.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_22_34.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1133338.196205624</v>
+        <v>1127988.399487807</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5877410.600141475</v>
+        <v>7024305.338384028</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12435573.96502165</v>
+        <v>14660963.01911776</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6571336.777159853</v>
+        <v>5754207.38569883</v>
       </c>
     </row>
     <row r="11">
@@ -8667,28 +8667,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>169.0966151720738</v>
+        <v>145.8327464505409</v>
       </c>
       <c r="K11" t="n">
-        <v>203.7259515474931</v>
+        <v>167.3144551584022</v>
       </c>
       <c r="L11" t="n">
-        <v>215.4655506483792</v>
+        <v>170.2938696529567</v>
       </c>
       <c r="M11" t="n">
-        <v>207.7576101116948</v>
+        <v>157.4954113531601</v>
       </c>
       <c r="N11" t="n">
-        <v>206.4589329433246</v>
+        <v>155.3834392613658</v>
       </c>
       <c r="O11" t="n">
-        <v>208.4232767483199</v>
+        <v>160.1941363949306</v>
       </c>
       <c r="P11" t="n">
-        <v>212.7339404788876</v>
+        <v>171.5714850078676</v>
       </c>
       <c r="Q11" t="n">
-        <v>208.413669773947</v>
+        <v>177.502379967731</v>
       </c>
       <c r="R11" t="n">
         <v>65.71641987298243</v>
@@ -8746,28 +8746,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J12" t="n">
-        <v>120.3346832704403</v>
+        <v>105.8649109507975</v>
       </c>
       <c r="K12" t="n">
-        <v>126.7268729366231</v>
+        <v>101.9957273309275</v>
       </c>
       <c r="L12" t="n">
-        <v>123.6094741194968</v>
+        <v>90.3553968397086</v>
       </c>
       <c r="M12" t="n">
-        <v>124.6940339220183</v>
+        <v>85.88809423000004</v>
       </c>
       <c r="N12" t="n">
-        <v>113.4401271776729</v>
+        <v>73.60710973268431</v>
       </c>
       <c r="O12" t="n">
-        <v>126.2197916142558</v>
+        <v>89.78036266371195</v>
       </c>
       <c r="P12" t="n">
-        <v>120.8308602445189</v>
+        <v>91.58500595490335</v>
       </c>
       <c r="Q12" t="n">
-        <v>131.1956608784743</v>
+        <v>111.6455817925041</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8831,19 +8831,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>126.3055287402547</v>
+        <v>107.2159712812904</v>
       </c>
       <c r="M13" t="n">
-        <v>129.8802757508838</v>
+        <v>109.753013963864</v>
       </c>
       <c r="N13" t="n">
-        <v>118.855118235725</v>
+        <v>99.20643774735849</v>
       </c>
       <c r="O13" t="n">
-        <v>130.3002105829903</v>
+        <v>112.1514739208908</v>
       </c>
       <c r="P13" t="n">
-        <v>130.748856508164</v>
+        <v>115.2194770025959</v>
       </c>
       <c r="Q13" t="n">
         <v>65.34295837775146</v>
@@ -8904,28 +8904,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>169.0966151720738</v>
+        <v>145.8327464505409</v>
       </c>
       <c r="K14" t="n">
-        <v>203.7259515474931</v>
+        <v>167.3144551584022</v>
       </c>
       <c r="L14" t="n">
-        <v>215.4655506483792</v>
+        <v>170.2938696529567</v>
       </c>
       <c r="M14" t="n">
-        <v>207.7576101116948</v>
+        <v>157.4954113531601</v>
       </c>
       <c r="N14" t="n">
-        <v>206.4589329433246</v>
+        <v>155.3834392613658</v>
       </c>
       <c r="O14" t="n">
-        <v>208.4232767483199</v>
+        <v>160.1941363949306</v>
       </c>
       <c r="P14" t="n">
-        <v>212.7339404788876</v>
+        <v>171.5714850078676</v>
       </c>
       <c r="Q14" t="n">
-        <v>208.413669773947</v>
+        <v>177.502379967731</v>
       </c>
       <c r="R14" t="n">
         <v>65.71641987298243</v>
@@ -8983,28 +8983,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J15" t="n">
-        <v>120.3346832704403</v>
+        <v>105.8649109507975</v>
       </c>
       <c r="K15" t="n">
-        <v>126.7268729366231</v>
+        <v>101.9957273309275</v>
       </c>
       <c r="L15" t="n">
-        <v>123.6094741194968</v>
+        <v>90.3553968397086</v>
       </c>
       <c r="M15" t="n">
-        <v>124.6940339220183</v>
+        <v>85.88809423000004</v>
       </c>
       <c r="N15" t="n">
-        <v>113.4401271776729</v>
+        <v>73.60710973268431</v>
       </c>
       <c r="O15" t="n">
-        <v>126.2197916142558</v>
+        <v>89.78036266371195</v>
       </c>
       <c r="P15" t="n">
-        <v>120.8308602445189</v>
+        <v>91.58500595490335</v>
       </c>
       <c r="Q15" t="n">
-        <v>131.1956608784743</v>
+        <v>111.6455817925041</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9068,19 +9068,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>126.3055287402547</v>
+        <v>107.2159712812904</v>
       </c>
       <c r="M16" t="n">
-        <v>129.8802757508838</v>
+        <v>109.753013963864</v>
       </c>
       <c r="N16" t="n">
-        <v>118.855118235725</v>
+        <v>99.20643774735849</v>
       </c>
       <c r="O16" t="n">
-        <v>130.3002105829903</v>
+        <v>112.1514739208908</v>
       </c>
       <c r="P16" t="n">
-        <v>130.748856508164</v>
+        <v>115.2194770025959</v>
       </c>
       <c r="Q16" t="n">
         <v>65.34295837775146</v>
@@ -9141,28 +9141,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>169.0966151720738</v>
+        <v>145.8327464505409</v>
       </c>
       <c r="K17" t="n">
-        <v>203.7259515474931</v>
+        <v>167.3144551584022</v>
       </c>
       <c r="L17" t="n">
-        <v>215.4655506483792</v>
+        <v>170.2938696529567</v>
       </c>
       <c r="M17" t="n">
-        <v>207.7576101116948</v>
+        <v>157.4954113531601</v>
       </c>
       <c r="N17" t="n">
-        <v>206.4589329433246</v>
+        <v>155.3834392613658</v>
       </c>
       <c r="O17" t="n">
-        <v>208.4232767483199</v>
+        <v>160.1941363949306</v>
       </c>
       <c r="P17" t="n">
-        <v>212.7339404788876</v>
+        <v>171.5714850078676</v>
       </c>
       <c r="Q17" t="n">
-        <v>208.413669773947</v>
+        <v>177.502379967731</v>
       </c>
       <c r="R17" t="n">
         <v>65.71641987298243</v>
@@ -9220,28 +9220,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J18" t="n">
-        <v>120.3346832704403</v>
+        <v>105.8649109507975</v>
       </c>
       <c r="K18" t="n">
-        <v>126.7268729366231</v>
+        <v>101.9957273309275</v>
       </c>
       <c r="L18" t="n">
-        <v>123.6094741194968</v>
+        <v>90.3553968397086</v>
       </c>
       <c r="M18" t="n">
-        <v>124.6940339220183</v>
+        <v>85.88809423000004</v>
       </c>
       <c r="N18" t="n">
-        <v>113.4401271776729</v>
+        <v>73.60710973268431</v>
       </c>
       <c r="O18" t="n">
-        <v>126.2197916142558</v>
+        <v>89.78036266371195</v>
       </c>
       <c r="P18" t="n">
-        <v>120.8308602445189</v>
+        <v>91.58500595490335</v>
       </c>
       <c r="Q18" t="n">
-        <v>131.1956608784743</v>
+        <v>111.6455817925041</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9305,19 +9305,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L19" t="n">
-        <v>126.3055287402547</v>
+        <v>107.2159712812904</v>
       </c>
       <c r="M19" t="n">
-        <v>129.8802757508838</v>
+        <v>109.753013963864</v>
       </c>
       <c r="N19" t="n">
-        <v>118.855118235725</v>
+        <v>99.20643774735849</v>
       </c>
       <c r="O19" t="n">
-        <v>130.3002105829903</v>
+        <v>112.1514739208908</v>
       </c>
       <c r="P19" t="n">
-        <v>130.748856508164</v>
+        <v>115.2194770025959</v>
       </c>
       <c r="Q19" t="n">
         <v>65.34295837775146</v>
@@ -9378,28 +9378,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>169.0966151720738</v>
+        <v>145.8327464505409</v>
       </c>
       <c r="K20" t="n">
-        <v>203.7259515474931</v>
+        <v>167.3144551584022</v>
       </c>
       <c r="L20" t="n">
-        <v>215.4655506483792</v>
+        <v>170.2938696529567</v>
       </c>
       <c r="M20" t="n">
-        <v>207.7576101116948</v>
+        <v>157.4954113531601</v>
       </c>
       <c r="N20" t="n">
-        <v>206.4589329433246</v>
+        <v>155.3834392613658</v>
       </c>
       <c r="O20" t="n">
-        <v>208.4232767483199</v>
+        <v>160.1941363949306</v>
       </c>
       <c r="P20" t="n">
-        <v>212.7339404788876</v>
+        <v>171.5714850078676</v>
       </c>
       <c r="Q20" t="n">
-        <v>208.413669773947</v>
+        <v>177.502379967731</v>
       </c>
       <c r="R20" t="n">
         <v>65.71641987298243</v>
@@ -9457,28 +9457,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J21" t="n">
-        <v>120.3346832704403</v>
+        <v>105.8649109507975</v>
       </c>
       <c r="K21" t="n">
-        <v>126.7268729366231</v>
+        <v>101.9957273309275</v>
       </c>
       <c r="L21" t="n">
-        <v>123.6094741194968</v>
+        <v>90.3553968397086</v>
       </c>
       <c r="M21" t="n">
-        <v>124.6940339220183</v>
+        <v>85.88809423000004</v>
       </c>
       <c r="N21" t="n">
-        <v>113.4401271776729</v>
+        <v>73.60710973268431</v>
       </c>
       <c r="O21" t="n">
-        <v>126.2197916142558</v>
+        <v>89.78036266371195</v>
       </c>
       <c r="P21" t="n">
-        <v>120.8308602445189</v>
+        <v>91.58500595490335</v>
       </c>
       <c r="Q21" t="n">
-        <v>131.1956608784743</v>
+        <v>111.6455817925041</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9542,19 +9542,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L22" t="n">
-        <v>126.3055287402547</v>
+        <v>107.2159712812904</v>
       </c>
       <c r="M22" t="n">
-        <v>129.8802757508838</v>
+        <v>109.753013963864</v>
       </c>
       <c r="N22" t="n">
-        <v>118.855118235725</v>
+        <v>99.20643774735849</v>
       </c>
       <c r="O22" t="n">
-        <v>130.3002105829903</v>
+        <v>112.1514739208908</v>
       </c>
       <c r="P22" t="n">
-        <v>130.748856508164</v>
+        <v>115.2194770025959</v>
       </c>
       <c r="Q22" t="n">
         <v>65.34295837775146</v>
@@ -9615,28 +9615,28 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>169.0966151720738</v>
+        <v>145.8327464505409</v>
       </c>
       <c r="K23" t="n">
-        <v>203.7259515474931</v>
+        <v>167.3144551584022</v>
       </c>
       <c r="L23" t="n">
-        <v>215.4655506483792</v>
+        <v>170.2938696529567</v>
       </c>
       <c r="M23" t="n">
-        <v>207.7576101116948</v>
+        <v>157.4954113531601</v>
       </c>
       <c r="N23" t="n">
-        <v>206.4589329433246</v>
+        <v>155.3834392613658</v>
       </c>
       <c r="O23" t="n">
-        <v>208.4232767483199</v>
+        <v>160.1941363949306</v>
       </c>
       <c r="P23" t="n">
-        <v>212.7339404788876</v>
+        <v>171.5714850078676</v>
       </c>
       <c r="Q23" t="n">
-        <v>208.413669773947</v>
+        <v>177.502379967731</v>
       </c>
       <c r="R23" t="n">
         <v>65.71641987298243</v>
@@ -9694,28 +9694,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J24" t="n">
-        <v>120.3346832704403</v>
+        <v>105.8649109507975</v>
       </c>
       <c r="K24" t="n">
-        <v>126.7268729366231</v>
+        <v>101.9957273309275</v>
       </c>
       <c r="L24" t="n">
-        <v>123.6094741194968</v>
+        <v>90.3553968397086</v>
       </c>
       <c r="M24" t="n">
-        <v>124.6940339220183</v>
+        <v>85.88809423000004</v>
       </c>
       <c r="N24" t="n">
-        <v>113.4401271776729</v>
+        <v>73.60710973268431</v>
       </c>
       <c r="O24" t="n">
-        <v>126.2197916142558</v>
+        <v>89.78036266371195</v>
       </c>
       <c r="P24" t="n">
-        <v>120.8308602445189</v>
+        <v>91.58500595490335</v>
       </c>
       <c r="Q24" t="n">
-        <v>131.1956608784743</v>
+        <v>111.6455817925041</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9779,19 +9779,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L25" t="n">
-        <v>126.3055287402547</v>
+        <v>107.2159712812904</v>
       </c>
       <c r="M25" t="n">
-        <v>129.8802757508838</v>
+        <v>109.753013963864</v>
       </c>
       <c r="N25" t="n">
-        <v>118.855118235725</v>
+        <v>99.20643774735849</v>
       </c>
       <c r="O25" t="n">
-        <v>130.3002105829903</v>
+        <v>112.1514739208908</v>
       </c>
       <c r="P25" t="n">
-        <v>130.748856508164</v>
+        <v>115.2194770025959</v>
       </c>
       <c r="Q25" t="n">
         <v>65.34295837775146</v>
@@ -9852,28 +9852,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>169.0966151720738</v>
+        <v>145.8327464505409</v>
       </c>
       <c r="K26" t="n">
-        <v>203.7259515474931</v>
+        <v>167.3144551584022</v>
       </c>
       <c r="L26" t="n">
-        <v>215.4655506483792</v>
+        <v>170.2938696529567</v>
       </c>
       <c r="M26" t="n">
-        <v>207.7576101116948</v>
+        <v>157.4954113531601</v>
       </c>
       <c r="N26" t="n">
-        <v>206.4589329433246</v>
+        <v>155.3834392613658</v>
       </c>
       <c r="O26" t="n">
-        <v>208.4232767483199</v>
+        <v>160.1941363949306</v>
       </c>
       <c r="P26" t="n">
-        <v>212.7339404788876</v>
+        <v>171.5714850078676</v>
       </c>
       <c r="Q26" t="n">
-        <v>208.413669773947</v>
+        <v>177.502379967731</v>
       </c>
       <c r="R26" t="n">
         <v>65.71641987298243</v>
@@ -9931,28 +9931,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J27" t="n">
-        <v>120.3346832704403</v>
+        <v>105.8649109507975</v>
       </c>
       <c r="K27" t="n">
-        <v>126.7268729366231</v>
+        <v>101.9957273309275</v>
       </c>
       <c r="L27" t="n">
-        <v>123.6094741194968</v>
+        <v>90.3553968397086</v>
       </c>
       <c r="M27" t="n">
-        <v>124.6940339220183</v>
+        <v>85.88809423000004</v>
       </c>
       <c r="N27" t="n">
-        <v>113.4401271776729</v>
+        <v>73.60710973268431</v>
       </c>
       <c r="O27" t="n">
-        <v>126.2197916142558</v>
+        <v>89.78036266371195</v>
       </c>
       <c r="P27" t="n">
-        <v>120.8308602445189</v>
+        <v>91.58500595490335</v>
       </c>
       <c r="Q27" t="n">
-        <v>131.1956608784743</v>
+        <v>111.6455817925041</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10016,19 +10016,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L28" t="n">
-        <v>126.3055287402547</v>
+        <v>107.2159712812904</v>
       </c>
       <c r="M28" t="n">
-        <v>129.8802757508838</v>
+        <v>109.753013963864</v>
       </c>
       <c r="N28" t="n">
-        <v>118.855118235725</v>
+        <v>99.20643774735849</v>
       </c>
       <c r="O28" t="n">
-        <v>130.3002105829903</v>
+        <v>112.1514739208908</v>
       </c>
       <c r="P28" t="n">
-        <v>130.748856508164</v>
+        <v>115.2194770025959</v>
       </c>
       <c r="Q28" t="n">
         <v>65.34295837775146</v>
@@ -10089,28 +10089,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>169.0966151720738</v>
+        <v>145.8327464505409</v>
       </c>
       <c r="K29" t="n">
-        <v>203.7259515474931</v>
+        <v>167.3144551584022</v>
       </c>
       <c r="L29" t="n">
-        <v>215.4655506483792</v>
+        <v>170.2938696529567</v>
       </c>
       <c r="M29" t="n">
-        <v>207.7576101116948</v>
+        <v>157.4954113531601</v>
       </c>
       <c r="N29" t="n">
-        <v>206.4589329433246</v>
+        <v>155.3834392613658</v>
       </c>
       <c r="O29" t="n">
-        <v>208.4232767483199</v>
+        <v>160.1941363949306</v>
       </c>
       <c r="P29" t="n">
-        <v>212.7339404788876</v>
+        <v>171.5714850078676</v>
       </c>
       <c r="Q29" t="n">
-        <v>208.413669773947</v>
+        <v>177.502379967731</v>
       </c>
       <c r="R29" t="n">
         <v>65.71641987298243</v>
@@ -10168,28 +10168,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J30" t="n">
-        <v>120.3346832704403</v>
+        <v>105.8649109507975</v>
       </c>
       <c r="K30" t="n">
-        <v>126.7268729366231</v>
+        <v>101.9957273309275</v>
       </c>
       <c r="L30" t="n">
-        <v>123.6094741194968</v>
+        <v>90.3553968397086</v>
       </c>
       <c r="M30" t="n">
-        <v>124.6940339220183</v>
+        <v>85.88809423000004</v>
       </c>
       <c r="N30" t="n">
-        <v>113.4401271776729</v>
+        <v>73.60710973268431</v>
       </c>
       <c r="O30" t="n">
-        <v>126.2197916142558</v>
+        <v>89.78036266371195</v>
       </c>
       <c r="P30" t="n">
-        <v>120.8308602445189</v>
+        <v>91.58500595490335</v>
       </c>
       <c r="Q30" t="n">
-        <v>131.1956608784743</v>
+        <v>111.6455817925041</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10253,19 +10253,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L31" t="n">
-        <v>126.3055287402547</v>
+        <v>107.2159712812904</v>
       </c>
       <c r="M31" t="n">
-        <v>129.8802757508838</v>
+        <v>109.753013963864</v>
       </c>
       <c r="N31" t="n">
-        <v>118.855118235725</v>
+        <v>99.20643774735849</v>
       </c>
       <c r="O31" t="n">
-        <v>130.3002105829903</v>
+        <v>112.1514739208908</v>
       </c>
       <c r="P31" t="n">
-        <v>130.748856508164</v>
+        <v>115.2194770025959</v>
       </c>
       <c r="Q31" t="n">
         <v>65.34295837775146</v>
@@ -10326,28 +10326,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>169.0966151720738</v>
+        <v>145.8327464505409</v>
       </c>
       <c r="K32" t="n">
-        <v>203.7259515474931</v>
+        <v>167.3144551584022</v>
       </c>
       <c r="L32" t="n">
-        <v>215.4655506483792</v>
+        <v>170.2938696529567</v>
       </c>
       <c r="M32" t="n">
-        <v>207.7576101116948</v>
+        <v>157.4954113531601</v>
       </c>
       <c r="N32" t="n">
-        <v>206.4589329433246</v>
+        <v>155.3834392613658</v>
       </c>
       <c r="O32" t="n">
-        <v>208.4232767483199</v>
+        <v>160.1941363949306</v>
       </c>
       <c r="P32" t="n">
-        <v>212.7339404788876</v>
+        <v>171.5714850078676</v>
       </c>
       <c r="Q32" t="n">
-        <v>208.413669773947</v>
+        <v>177.502379967731</v>
       </c>
       <c r="R32" t="n">
         <v>65.71641987298243</v>
@@ -10405,28 +10405,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J33" t="n">
-        <v>120.3346832704403</v>
+        <v>105.8649109507975</v>
       </c>
       <c r="K33" t="n">
-        <v>126.7268729366231</v>
+        <v>101.9957273309275</v>
       </c>
       <c r="L33" t="n">
-        <v>123.6094741194968</v>
+        <v>90.3553968397086</v>
       </c>
       <c r="M33" t="n">
-        <v>124.6940339220183</v>
+        <v>85.88809423000004</v>
       </c>
       <c r="N33" t="n">
-        <v>113.4401271776729</v>
+        <v>73.60710973268431</v>
       </c>
       <c r="O33" t="n">
-        <v>126.2197916142558</v>
+        <v>89.78036266371195</v>
       </c>
       <c r="P33" t="n">
-        <v>120.8308602445189</v>
+        <v>91.58500595490335</v>
       </c>
       <c r="Q33" t="n">
-        <v>131.1956608784743</v>
+        <v>111.6455817925041</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10490,19 +10490,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L34" t="n">
-        <v>126.3055287402547</v>
+        <v>107.2159712812904</v>
       </c>
       <c r="M34" t="n">
-        <v>129.8802757508838</v>
+        <v>109.753013963864</v>
       </c>
       <c r="N34" t="n">
-        <v>118.855118235725</v>
+        <v>99.20643774735849</v>
       </c>
       <c r="O34" t="n">
-        <v>130.3002105829903</v>
+        <v>112.1514739208908</v>
       </c>
       <c r="P34" t="n">
-        <v>130.748856508164</v>
+        <v>115.2194770025959</v>
       </c>
       <c r="Q34" t="n">
         <v>65.34295837775146</v>
@@ -10563,28 +10563,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>169.0966151720738</v>
+        <v>145.8327464505409</v>
       </c>
       <c r="K35" t="n">
-        <v>203.7259515474931</v>
+        <v>167.3144551584022</v>
       </c>
       <c r="L35" t="n">
-        <v>215.4655506483792</v>
+        <v>170.2938696529567</v>
       </c>
       <c r="M35" t="n">
-        <v>207.7576101116948</v>
+        <v>157.4954113531601</v>
       </c>
       <c r="N35" t="n">
-        <v>206.4589329433246</v>
+        <v>155.3834392613658</v>
       </c>
       <c r="O35" t="n">
-        <v>208.4232767483199</v>
+        <v>160.1941363949306</v>
       </c>
       <c r="P35" t="n">
-        <v>212.7339404788876</v>
+        <v>171.5714850078676</v>
       </c>
       <c r="Q35" t="n">
-        <v>208.413669773947</v>
+        <v>177.502379967731</v>
       </c>
       <c r="R35" t="n">
         <v>65.71641987298243</v>
@@ -10642,28 +10642,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J36" t="n">
-        <v>120.3346832704403</v>
+        <v>105.8649109507975</v>
       </c>
       <c r="K36" t="n">
-        <v>126.7268729366231</v>
+        <v>101.9957273309275</v>
       </c>
       <c r="L36" t="n">
-        <v>123.6094741194968</v>
+        <v>90.3553968397086</v>
       </c>
       <c r="M36" t="n">
-        <v>124.6940339220183</v>
+        <v>85.88809423000004</v>
       </c>
       <c r="N36" t="n">
-        <v>113.4401271776729</v>
+        <v>73.60710973268431</v>
       </c>
       <c r="O36" t="n">
-        <v>126.2197916142558</v>
+        <v>89.78036266371195</v>
       </c>
       <c r="P36" t="n">
-        <v>120.8308602445189</v>
+        <v>91.58500595490335</v>
       </c>
       <c r="Q36" t="n">
-        <v>131.1956608784743</v>
+        <v>111.6455817925041</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10727,19 +10727,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L37" t="n">
-        <v>126.3055287402547</v>
+        <v>107.2159712812904</v>
       </c>
       <c r="M37" t="n">
-        <v>129.8802757508838</v>
+        <v>109.753013963864</v>
       </c>
       <c r="N37" t="n">
-        <v>118.855118235725</v>
+        <v>99.20643774735849</v>
       </c>
       <c r="O37" t="n">
-        <v>130.3002105829903</v>
+        <v>112.1514739208908</v>
       </c>
       <c r="P37" t="n">
-        <v>130.748856508164</v>
+        <v>115.2194770025959</v>
       </c>
       <c r="Q37" t="n">
         <v>65.34295837775146</v>
@@ -10800,28 +10800,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>169.0966151720738</v>
+        <v>145.8327464505409</v>
       </c>
       <c r="K38" t="n">
-        <v>203.7259515474931</v>
+        <v>167.3144551584022</v>
       </c>
       <c r="L38" t="n">
-        <v>215.4655506483792</v>
+        <v>170.2938696529567</v>
       </c>
       <c r="M38" t="n">
-        <v>207.7576101116948</v>
+        <v>157.4954113531601</v>
       </c>
       <c r="N38" t="n">
-        <v>206.4589329433246</v>
+        <v>155.3834392613658</v>
       </c>
       <c r="O38" t="n">
-        <v>208.4232767483199</v>
+        <v>160.1941363949306</v>
       </c>
       <c r="P38" t="n">
-        <v>212.7339404788876</v>
+        <v>171.5714850078676</v>
       </c>
       <c r="Q38" t="n">
-        <v>208.413669773947</v>
+        <v>177.502379967731</v>
       </c>
       <c r="R38" t="n">
         <v>65.71641987298243</v>
@@ -10879,28 +10879,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J39" t="n">
-        <v>120.3346832704403</v>
+        <v>105.8649109507975</v>
       </c>
       <c r="K39" t="n">
-        <v>126.7268729366231</v>
+        <v>101.9957273309275</v>
       </c>
       <c r="L39" t="n">
-        <v>123.6094741194968</v>
+        <v>90.3553968397086</v>
       </c>
       <c r="M39" t="n">
-        <v>124.6940339220183</v>
+        <v>85.88809423000004</v>
       </c>
       <c r="N39" t="n">
-        <v>113.4401271776729</v>
+        <v>73.60710973268431</v>
       </c>
       <c r="O39" t="n">
-        <v>126.2197916142558</v>
+        <v>89.78036266371195</v>
       </c>
       <c r="P39" t="n">
-        <v>120.8308602445189</v>
+        <v>91.58500595490335</v>
       </c>
       <c r="Q39" t="n">
-        <v>131.1956608784743</v>
+        <v>111.6455817925041</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10964,19 +10964,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L40" t="n">
-        <v>126.3055287402547</v>
+        <v>107.2159712812904</v>
       </c>
       <c r="M40" t="n">
-        <v>129.8802757508838</v>
+        <v>109.753013963864</v>
       </c>
       <c r="N40" t="n">
-        <v>118.855118235725</v>
+        <v>99.20643774735849</v>
       </c>
       <c r="O40" t="n">
-        <v>130.3002105829903</v>
+        <v>112.1514739208908</v>
       </c>
       <c r="P40" t="n">
-        <v>130.748856508164</v>
+        <v>115.2194770025959</v>
       </c>
       <c r="Q40" t="n">
         <v>65.34295837775146</v>
@@ -11037,28 +11037,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>169.0966151720738</v>
+        <v>145.8327464505409</v>
       </c>
       <c r="K41" t="n">
-        <v>203.7259515474931</v>
+        <v>167.3144551584022</v>
       </c>
       <c r="L41" t="n">
-        <v>215.4655506483792</v>
+        <v>170.2938696529567</v>
       </c>
       <c r="M41" t="n">
-        <v>207.7576101116948</v>
+        <v>157.4954113531601</v>
       </c>
       <c r="N41" t="n">
-        <v>206.4589329433246</v>
+        <v>155.3834392613658</v>
       </c>
       <c r="O41" t="n">
-        <v>208.4232767483199</v>
+        <v>160.1941363949306</v>
       </c>
       <c r="P41" t="n">
-        <v>212.7339404788876</v>
+        <v>171.5714850078676</v>
       </c>
       <c r="Q41" t="n">
-        <v>208.413669773947</v>
+        <v>177.502379967731</v>
       </c>
       <c r="R41" t="n">
         <v>65.71641987298243</v>
@@ -11116,28 +11116,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J42" t="n">
-        <v>120.3346832704403</v>
+        <v>105.8649109507975</v>
       </c>
       <c r="K42" t="n">
-        <v>126.7268729366231</v>
+        <v>101.9957273309275</v>
       </c>
       <c r="L42" t="n">
-        <v>123.6094741194968</v>
+        <v>90.3553968397086</v>
       </c>
       <c r="M42" t="n">
-        <v>124.6940339220183</v>
+        <v>85.88809423000004</v>
       </c>
       <c r="N42" t="n">
-        <v>113.4401271776729</v>
+        <v>73.60710973268431</v>
       </c>
       <c r="O42" t="n">
-        <v>126.2197916142558</v>
+        <v>89.78036266371195</v>
       </c>
       <c r="P42" t="n">
-        <v>120.8308602445189</v>
+        <v>91.58500595490335</v>
       </c>
       <c r="Q42" t="n">
-        <v>131.1956608784743</v>
+        <v>111.6455817925041</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11201,19 +11201,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L43" t="n">
-        <v>126.3055287402547</v>
+        <v>107.2159712812904</v>
       </c>
       <c r="M43" t="n">
-        <v>129.8802757508838</v>
+        <v>109.753013963864</v>
       </c>
       <c r="N43" t="n">
-        <v>118.855118235725</v>
+        <v>99.20643774735849</v>
       </c>
       <c r="O43" t="n">
-        <v>130.3002105829903</v>
+        <v>112.1514739208908</v>
       </c>
       <c r="P43" t="n">
-        <v>130.748856508164</v>
+        <v>115.2194770025959</v>
       </c>
       <c r="Q43" t="n">
         <v>65.34295837775146</v>
@@ -11274,28 +11274,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>169.0966151720738</v>
+        <v>145.8327464505409</v>
       </c>
       <c r="K44" t="n">
-        <v>203.7259515474931</v>
+        <v>167.3144551584022</v>
       </c>
       <c r="L44" t="n">
-        <v>215.4655506483792</v>
+        <v>170.2938696529567</v>
       </c>
       <c r="M44" t="n">
-        <v>207.7576101116948</v>
+        <v>157.4954113531601</v>
       </c>
       <c r="N44" t="n">
-        <v>206.4589329433246</v>
+        <v>155.3834392613658</v>
       </c>
       <c r="O44" t="n">
-        <v>208.4232767483199</v>
+        <v>160.1941363949306</v>
       </c>
       <c r="P44" t="n">
-        <v>212.7339404788876</v>
+        <v>171.5714850078676</v>
       </c>
       <c r="Q44" t="n">
-        <v>208.413669773947</v>
+        <v>177.502379967731</v>
       </c>
       <c r="R44" t="n">
         <v>65.71641987298243</v>
@@ -11353,28 +11353,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J45" t="n">
-        <v>120.3346832704403</v>
+        <v>105.8649109507975</v>
       </c>
       <c r="K45" t="n">
-        <v>126.7268729366231</v>
+        <v>101.9957273309275</v>
       </c>
       <c r="L45" t="n">
-        <v>123.6094741194968</v>
+        <v>90.3553968397086</v>
       </c>
       <c r="M45" t="n">
-        <v>124.6940339220183</v>
+        <v>85.88809423000004</v>
       </c>
       <c r="N45" t="n">
-        <v>113.4401271776729</v>
+        <v>73.60710973268431</v>
       </c>
       <c r="O45" t="n">
-        <v>126.2197916142558</v>
+        <v>89.78036266371195</v>
       </c>
       <c r="P45" t="n">
-        <v>120.8308602445189</v>
+        <v>91.58500595490335</v>
       </c>
       <c r="Q45" t="n">
-        <v>131.1956608784743</v>
+        <v>111.6455817925041</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -11438,19 +11438,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L46" t="n">
-        <v>126.3055287402547</v>
+        <v>107.2159712812904</v>
       </c>
       <c r="M46" t="n">
-        <v>129.8802757508838</v>
+        <v>109.753013963864</v>
       </c>
       <c r="N46" t="n">
-        <v>118.855118235725</v>
+        <v>99.20643774735849</v>
       </c>
       <c r="O46" t="n">
-        <v>130.3002105829903</v>
+        <v>112.1514739208908</v>
       </c>
       <c r="P46" t="n">
-        <v>130.748856508164</v>
+        <v>115.2194770025959</v>
       </c>
       <c r="Q46" t="n">
         <v>65.34295837775146</v>
@@ -23215,31 +23215,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>381.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C11" t="n">
-        <v>364.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D11" t="n">
-        <v>353.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E11" t="n">
-        <v>380.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F11" t="n">
-        <v>405.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>414.1740942990557</v>
+        <v>414.887848835465</v>
       </c>
       <c r="H11" t="n">
-        <v>337.1573347790837</v>
+        <v>335.2258234250963</v>
       </c>
       <c r="I11" t="n">
-        <v>204.5163719824662</v>
+        <v>194.4808937474265</v>
       </c>
       <c r="J11" t="n">
-        <v>0.03085719380743512</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -23263,28 +23263,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>140.7882335190391</v>
+        <v>123.8073669168263</v>
       </c>
       <c r="S11" t="n">
-        <v>205.0886122998132</v>
+        <v>199.5657937982642</v>
       </c>
       <c r="T11" t="n">
-        <v>221.5327138857394</v>
+        <v>221.2796743688757</v>
       </c>
       <c r="U11" t="n">
-        <v>250.3353614505501</v>
+        <v>251.3124618134629</v>
       </c>
       <c r="V11" t="n">
-        <v>326.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W11" t="n">
-        <v>348.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X11" t="n">
-        <v>368.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y11" t="n">
-        <v>385.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="12">
@@ -23294,28 +23294,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>165.5331836498673</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C12" t="n">
-        <v>171.7084989883157</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D12" t="n">
-        <v>146.4450655646388</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E12" t="n">
-        <v>156.6450804554009</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F12" t="n">
-        <v>144.0692123933839</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>136.2746869745314</v>
+        <v>137.1215321493664</v>
       </c>
       <c r="H12" t="n">
-        <v>110.5706895195153</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="I12" t="n">
-        <v>86.02682153066036</v>
+        <v>81.7537277694981</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,28 +23342,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>94.88432471868087</v>
+        <v>86.37529092466649</v>
       </c>
       <c r="S12" t="n">
-        <v>169.4046805378001</v>
+        <v>167.5598968335298</v>
       </c>
       <c r="T12" t="n">
-        <v>198.8872947325575</v>
+        <v>199.2699733100723</v>
       </c>
       <c r="U12" t="n">
-        <v>224.936853779088</v>
+        <v>225.9267778037482</v>
       </c>
       <c r="V12" t="n">
-        <v>231.8005871494253</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W12" t="n">
-        <v>250.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X12" t="n">
-        <v>204.7729852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y12" t="n">
-        <v>204.6826957773044</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="13">
@@ -23373,34 +23373,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>178.8319801819373</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C13" t="n">
-        <v>166.2468210986278</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D13" t="n">
-        <v>147.6154730182124</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E13" t="n">
-        <v>145.4339626465692</v>
+        <v>146.4339626465692</v>
       </c>
       <c r="F13" t="n">
-        <v>144.4210480229312</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>166.933274440426</v>
+        <v>167.8048745798117</v>
       </c>
       <c r="H13" t="n">
-        <v>160.7141233271117</v>
+        <v>160.5725318391047</v>
       </c>
       <c r="I13" t="n">
-        <v>152.7151306649632</v>
+        <v>149.8537966748535</v>
       </c>
       <c r="J13" t="n">
-        <v>88.27944241175474</v>
+        <v>80.20157226632458</v>
       </c>
       <c r="K13" t="n">
-        <v>14.56522953080089</v>
+        <v>0.6475002703408634</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23418,31 +23418,31 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>80.33004325169439</v>
+        <v>70.57830583243795</v>
       </c>
       <c r="R13" t="n">
-        <v>173.6987684263498</v>
+        <v>168.9254437845474</v>
       </c>
       <c r="S13" t="n">
-        <v>222.0109586927099</v>
+        <v>220.773299303641</v>
       </c>
       <c r="T13" t="n">
-        <v>226.6990320512323</v>
+        <v>227.1504144649713</v>
       </c>
       <c r="U13" t="n">
-        <v>285.3158818155073</v>
+        <v>286.3088781867465</v>
       </c>
       <c r="V13" t="n">
-        <v>251.137643323828</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W13" t="n">
-        <v>285.522998336591</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X13" t="n">
-        <v>224.7096553890372</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y13" t="n">
-        <v>217.5846533520948</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="14">
@@ -23452,28 +23452,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>304.7338416634806</v>
+        <v>382.0863413931397</v>
       </c>
       <c r="C14" t="n">
-        <v>287.2728917710076</v>
+        <v>364.6253915006667</v>
       </c>
       <c r="D14" t="n">
-        <v>276.683041620683</v>
+        <v>354.0355413503421</v>
       </c>
       <c r="E14" t="n">
-        <v>303.9303700722618</v>
+        <v>381.2828698019209</v>
       </c>
       <c r="F14" t="n">
-        <v>328.8760457417114</v>
+        <v>406.2285454713706</v>
       </c>
       <c r="G14" t="n">
-        <v>337.1740942990547</v>
+        <v>414.2403485651241</v>
       </c>
       <c r="H14" t="n">
-        <v>260.1573347790837</v>
+        <v>334.5783231547555</v>
       </c>
       <c r="I14" t="n">
-        <v>127.5163719824662</v>
+        <v>193.8333934770857</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,28 +23500,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>63.78823351903912</v>
+        <v>123.1598666464854</v>
       </c>
       <c r="S14" t="n">
-        <v>128.0886122998132</v>
+        <v>198.9182935279234</v>
       </c>
       <c r="T14" t="n">
-        <v>144.5327138857394</v>
+        <v>220.6321740985349</v>
       </c>
       <c r="U14" t="n">
-        <v>173.3353614505501</v>
+        <v>250.664961543122</v>
       </c>
       <c r="V14" t="n">
-        <v>249.7522584701349</v>
+        <v>327.104758199794</v>
       </c>
       <c r="W14" t="n">
-        <v>271.240968717413</v>
+        <v>348.5934684470722</v>
       </c>
       <c r="X14" t="n">
-        <v>291.731100678469</v>
+        <v>369.0836004081282</v>
       </c>
       <c r="Y14" t="n">
-        <v>308.2379386560536</v>
+        <v>385.5904383857127</v>
       </c>
     </row>
     <row r="15">
@@ -23531,28 +23531,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>88.53318364986734</v>
+        <v>165.8856833795265</v>
       </c>
       <c r="C15" t="n">
-        <v>94.70849898831574</v>
+        <v>172.0609987179749</v>
       </c>
       <c r="D15" t="n">
-        <v>69.44506556463875</v>
+        <v>146.7975652942979</v>
       </c>
       <c r="E15" t="n">
-        <v>79.64508045540094</v>
+        <v>156.9975801850601</v>
       </c>
       <c r="F15" t="n">
-        <v>67.06921239338388</v>
+        <v>144.421712123043</v>
       </c>
       <c r="G15" t="n">
-        <v>59.27468697453139</v>
+        <v>136.4740318790256</v>
       </c>
       <c r="H15" t="n">
-        <v>33.57068951951533</v>
+        <v>109.4440360692917</v>
       </c>
       <c r="I15" t="n">
-        <v>9.02682153066036</v>
+        <v>81.10622749915723</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23579,28 +23579,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>17.88432471868087</v>
+        <v>85.72779065432562</v>
       </c>
       <c r="S15" t="n">
-        <v>92.40468053780009</v>
+        <v>166.9123965631889</v>
       </c>
       <c r="T15" t="n">
-        <v>121.8872947325575</v>
+        <v>198.6224730397315</v>
       </c>
       <c r="U15" t="n">
-        <v>147.936853779088</v>
+        <v>225.2792775334074</v>
       </c>
       <c r="V15" t="n">
-        <v>154.8005871494253</v>
+        <v>232.1530868790844</v>
       </c>
       <c r="W15" t="n">
-        <v>173.6949831609196</v>
+        <v>251.0474828905787</v>
       </c>
       <c r="X15" t="n">
-        <v>127.7729852034775</v>
+        <v>205.1254849331366</v>
       </c>
       <c r="Y15" t="n">
-        <v>127.6826957773044</v>
+        <v>205.0351955069635</v>
       </c>
     </row>
     <row r="16">
@@ -23610,31 +23610,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>101.8319801819373</v>
+        <v>179.1844799115964</v>
       </c>
       <c r="C16" t="n">
-        <v>89.24682109862783</v>
+        <v>166.599320828287</v>
       </c>
       <c r="D16" t="n">
-        <v>70.61547301821236</v>
+        <v>147.9679727478715</v>
       </c>
       <c r="E16" t="n">
-        <v>68.43396264656917</v>
+        <v>145.7864623762283</v>
       </c>
       <c r="F16" t="n">
-        <v>67.42104802293125</v>
+        <v>144.7735477525904</v>
       </c>
       <c r="G16" t="n">
-        <v>89.93327444042598</v>
+        <v>167.1573743094708</v>
       </c>
       <c r="H16" t="n">
-        <v>83.71412332711171</v>
+        <v>159.9250315687638</v>
       </c>
       <c r="I16" t="n">
-        <v>75.7151306649632</v>
+        <v>149.2062964045127</v>
       </c>
       <c r="J16" t="n">
-        <v>11.27944241175474</v>
+        <v>79.5540719959837</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23655,31 +23655,31 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.330043251694385</v>
+        <v>69.93080556209708</v>
       </c>
       <c r="R16" t="n">
-        <v>96.69876842634982</v>
+        <v>168.2779435142065</v>
       </c>
       <c r="S16" t="n">
-        <v>145.0109586927099</v>
+        <v>220.1257990333001</v>
       </c>
       <c r="T16" t="n">
-        <v>149.6990320512323</v>
+        <v>226.5029141946304</v>
       </c>
       <c r="U16" t="n">
-        <v>208.3158818155073</v>
+        <v>285.6613779164056</v>
       </c>
       <c r="V16" t="n">
-        <v>174.137643323828</v>
+        <v>251.4901430534871</v>
       </c>
       <c r="W16" t="n">
-        <v>208.522998336591</v>
+        <v>285.8754980662501</v>
       </c>
       <c r="X16" t="n">
-        <v>147.7096553890372</v>
+        <v>225.0621551186963</v>
       </c>
       <c r="Y16" t="n">
-        <v>140.5846533520948</v>
+        <v>217.9371530817539</v>
       </c>
     </row>
     <row r="17">
@@ -23689,28 +23689,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>304.7338416634806</v>
+        <v>382.0863413931397</v>
       </c>
       <c r="C17" t="n">
-        <v>287.2728917710076</v>
+        <v>364.6253915006667</v>
       </c>
       <c r="D17" t="n">
-        <v>276.683041620683</v>
+        <v>354.0355413503421</v>
       </c>
       <c r="E17" t="n">
-        <v>303.9303700722618</v>
+        <v>381.2828698019209</v>
       </c>
       <c r="F17" t="n">
-        <v>328.8760457417114</v>
+        <v>406.2285454713706</v>
       </c>
       <c r="G17" t="n">
-        <v>337.1740942990547</v>
+        <v>414.2403485651241</v>
       </c>
       <c r="H17" t="n">
-        <v>260.1573347790837</v>
+        <v>334.5783231547555</v>
       </c>
       <c r="I17" t="n">
-        <v>127.5163719824662</v>
+        <v>193.8333934770857</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,28 +23737,28 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>63.78823351903912</v>
+        <v>123.1598666464854</v>
       </c>
       <c r="S17" t="n">
-        <v>128.0886122998132</v>
+        <v>198.9182935279234</v>
       </c>
       <c r="T17" t="n">
-        <v>144.5327138857394</v>
+        <v>220.6321740985349</v>
       </c>
       <c r="U17" t="n">
-        <v>173.3353614505501</v>
+        <v>250.664961543122</v>
       </c>
       <c r="V17" t="n">
-        <v>249.7522584701349</v>
+        <v>327.104758199794</v>
       </c>
       <c r="W17" t="n">
-        <v>271.240968717413</v>
+        <v>348.5934684470722</v>
       </c>
       <c r="X17" t="n">
-        <v>291.731100678469</v>
+        <v>369.0836004081282</v>
       </c>
       <c r="Y17" t="n">
-        <v>308.2379386560536</v>
+        <v>385.5904383857127</v>
       </c>
     </row>
     <row r="18">
@@ -23768,28 +23768,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>88.53318364986734</v>
+        <v>165.8856833795265</v>
       </c>
       <c r="C18" t="n">
-        <v>94.70849898831574</v>
+        <v>172.0609987179749</v>
       </c>
       <c r="D18" t="n">
-        <v>69.44506556463875</v>
+        <v>146.7975652942979</v>
       </c>
       <c r="E18" t="n">
-        <v>79.64508045540094</v>
+        <v>156.9975801850601</v>
       </c>
       <c r="F18" t="n">
-        <v>67.06921239338388</v>
+        <v>144.421712123043</v>
       </c>
       <c r="G18" t="n">
-        <v>59.27468697453139</v>
+        <v>136.4740318790256</v>
       </c>
       <c r="H18" t="n">
-        <v>33.57068951951533</v>
+        <v>109.4440360692917</v>
       </c>
       <c r="I18" t="n">
-        <v>9.02682153066036</v>
+        <v>81.10622749915723</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -23816,28 +23816,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>17.88432471868087</v>
+        <v>85.72779065432562</v>
       </c>
       <c r="S18" t="n">
-        <v>92.40468053780009</v>
+        <v>166.9123965631889</v>
       </c>
       <c r="T18" t="n">
-        <v>121.8872947325575</v>
+        <v>198.6224730397315</v>
       </c>
       <c r="U18" t="n">
-        <v>147.936853779088</v>
+        <v>225.2792775334074</v>
       </c>
       <c r="V18" t="n">
-        <v>154.8005871494253</v>
+        <v>232.1530868790844</v>
       </c>
       <c r="W18" t="n">
-        <v>173.6949831609196</v>
+        <v>251.0474828905787</v>
       </c>
       <c r="X18" t="n">
-        <v>127.7729852034775</v>
+        <v>205.1254849331366</v>
       </c>
       <c r="Y18" t="n">
-        <v>127.6826957773044</v>
+        <v>205.0351955069635</v>
       </c>
     </row>
     <row r="19">
@@ -23847,31 +23847,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>101.8319801819373</v>
+        <v>179.1844799115964</v>
       </c>
       <c r="C19" t="n">
-        <v>89.24682109862783</v>
+        <v>166.599320828287</v>
       </c>
       <c r="D19" t="n">
-        <v>70.61547301821236</v>
+        <v>147.9679727478715</v>
       </c>
       <c r="E19" t="n">
-        <v>68.43396264656917</v>
+        <v>145.7864623762283</v>
       </c>
       <c r="F19" t="n">
-        <v>67.42104802293125</v>
+        <v>144.7735477525904</v>
       </c>
       <c r="G19" t="n">
-        <v>89.93327444042598</v>
+        <v>167.1573743094708</v>
       </c>
       <c r="H19" t="n">
-        <v>83.71412332711171</v>
+        <v>159.9250315687638</v>
       </c>
       <c r="I19" t="n">
-        <v>75.7151306649632</v>
+        <v>149.2062964045127</v>
       </c>
       <c r="J19" t="n">
-        <v>11.27944241175474</v>
+        <v>79.5540719959837</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -23892,31 +23892,31 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.330043251694385</v>
+        <v>69.93080556209708</v>
       </c>
       <c r="R19" t="n">
-        <v>96.69876842634982</v>
+        <v>168.2779435142065</v>
       </c>
       <c r="S19" t="n">
-        <v>145.0109586927099</v>
+        <v>220.1257990333001</v>
       </c>
       <c r="T19" t="n">
-        <v>149.6990320512323</v>
+        <v>226.5029141946304</v>
       </c>
       <c r="U19" t="n">
-        <v>208.3158818155073</v>
+        <v>285.6613779164056</v>
       </c>
       <c r="V19" t="n">
-        <v>174.137643323828</v>
+        <v>251.4901430534871</v>
       </c>
       <c r="W19" t="n">
-        <v>208.522998336591</v>
+        <v>285.8754980662501</v>
       </c>
       <c r="X19" t="n">
-        <v>147.7096553890372</v>
+        <v>225.0621551186963</v>
       </c>
       <c r="Y19" t="n">
-        <v>140.5846533520948</v>
+        <v>217.9371530817539</v>
       </c>
     </row>
     <row r="20">
@@ -23926,28 +23926,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>304.7338416634806</v>
+        <v>382.0863413931397</v>
       </c>
       <c r="C20" t="n">
-        <v>287.2728917710076</v>
+        <v>364.6253915006667</v>
       </c>
       <c r="D20" t="n">
-        <v>276.683041620683</v>
+        <v>354.0355413503421</v>
       </c>
       <c r="E20" t="n">
-        <v>303.9303700722618</v>
+        <v>381.2828698019209</v>
       </c>
       <c r="F20" t="n">
-        <v>328.8760457417114</v>
+        <v>406.2285454713706</v>
       </c>
       <c r="G20" t="n">
-        <v>337.1740942990547</v>
+        <v>414.2403485651241</v>
       </c>
       <c r="H20" t="n">
-        <v>260.1573347790837</v>
+        <v>334.5783231547555</v>
       </c>
       <c r="I20" t="n">
-        <v>127.5163719824662</v>
+        <v>193.8333934770857</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,28 +23974,28 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>63.78823351903912</v>
+        <v>123.1598666464854</v>
       </c>
       <c r="S20" t="n">
-        <v>128.0886122998132</v>
+        <v>198.9182935279234</v>
       </c>
       <c r="T20" t="n">
-        <v>144.5327138857394</v>
+        <v>220.6321740985349</v>
       </c>
       <c r="U20" t="n">
-        <v>173.3353614505501</v>
+        <v>250.664961543122</v>
       </c>
       <c r="V20" t="n">
-        <v>249.7522584701349</v>
+        <v>327.104758199794</v>
       </c>
       <c r="W20" t="n">
-        <v>271.240968717413</v>
+        <v>348.5934684470722</v>
       </c>
       <c r="X20" t="n">
-        <v>291.731100678469</v>
+        <v>369.0836004081282</v>
       </c>
       <c r="Y20" t="n">
-        <v>308.2379386560536</v>
+        <v>385.5904383857127</v>
       </c>
     </row>
     <row r="21">
@@ -24005,28 +24005,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>88.53318364986734</v>
+        <v>165.8856833795265</v>
       </c>
       <c r="C21" t="n">
-        <v>94.70849898831574</v>
+        <v>172.0609987179749</v>
       </c>
       <c r="D21" t="n">
-        <v>69.44506556463875</v>
+        <v>146.7975652942979</v>
       </c>
       <c r="E21" t="n">
-        <v>79.64508045540094</v>
+        <v>156.9975801850601</v>
       </c>
       <c r="F21" t="n">
-        <v>67.06921239338388</v>
+        <v>144.421712123043</v>
       </c>
       <c r="G21" t="n">
-        <v>59.27468697453139</v>
+        <v>136.4740318790256</v>
       </c>
       <c r="H21" t="n">
-        <v>33.57068951951533</v>
+        <v>109.4440360692917</v>
       </c>
       <c r="I21" t="n">
-        <v>9.026821530660357</v>
+        <v>81.10622749915723</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -24053,28 +24053,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>17.88432471868087</v>
+        <v>85.72779065432562</v>
       </c>
       <c r="S21" t="n">
-        <v>92.40468053780009</v>
+        <v>166.9123965631889</v>
       </c>
       <c r="T21" t="n">
-        <v>121.8872947325575</v>
+        <v>198.6224730397315</v>
       </c>
       <c r="U21" t="n">
-        <v>147.936853779088</v>
+        <v>225.2792775334074</v>
       </c>
       <c r="V21" t="n">
-        <v>154.8005871494253</v>
+        <v>232.1530868790844</v>
       </c>
       <c r="W21" t="n">
-        <v>173.6949831609196</v>
+        <v>251.0474828905787</v>
       </c>
       <c r="X21" t="n">
-        <v>127.7729852034775</v>
+        <v>205.1254849331366</v>
       </c>
       <c r="Y21" t="n">
-        <v>127.6826957773044</v>
+        <v>205.0351955069635</v>
       </c>
     </row>
     <row r="22">
@@ -24084,31 +24084,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>101.8319801819373</v>
+        <v>179.1844799115964</v>
       </c>
       <c r="C22" t="n">
-        <v>89.24682109862783</v>
+        <v>166.599320828287</v>
       </c>
       <c r="D22" t="n">
-        <v>70.61547301821236</v>
+        <v>147.9679727478715</v>
       </c>
       <c r="E22" t="n">
-        <v>68.43396264656917</v>
+        <v>145.7864623762283</v>
       </c>
       <c r="F22" t="n">
-        <v>67.42104802293125</v>
+        <v>144.7735477525904</v>
       </c>
       <c r="G22" t="n">
-        <v>89.93327444042598</v>
+        <v>167.1573743094708</v>
       </c>
       <c r="H22" t="n">
-        <v>83.71412332711171</v>
+        <v>159.9250315687638</v>
       </c>
       <c r="I22" t="n">
-        <v>75.7151306649632</v>
+        <v>149.2062964045127</v>
       </c>
       <c r="J22" t="n">
-        <v>11.27944241175474</v>
+        <v>79.5540719959837</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -24129,31 +24129,31 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.330043251694391</v>
+        <v>69.93080556209708</v>
       </c>
       <c r="R22" t="n">
-        <v>96.6987684263498</v>
+        <v>168.2779435142065</v>
       </c>
       <c r="S22" t="n">
-        <v>145.0109586927099</v>
+        <v>220.1257990333001</v>
       </c>
       <c r="T22" t="n">
-        <v>149.6990320512323</v>
+        <v>226.5029141946304</v>
       </c>
       <c r="U22" t="n">
-        <v>208.3158818155073</v>
+        <v>285.6613779164056</v>
       </c>
       <c r="V22" t="n">
-        <v>174.137643323828</v>
+        <v>251.4901430534871</v>
       </c>
       <c r="W22" t="n">
-        <v>208.522998336591</v>
+        <v>285.8754980662501</v>
       </c>
       <c r="X22" t="n">
-        <v>147.7096553890372</v>
+        <v>225.0621551186963</v>
       </c>
       <c r="Y22" t="n">
-        <v>140.5846533520948</v>
+        <v>217.9371530817539</v>
       </c>
     </row>
     <row r="23">
@@ -24163,28 +24163,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>304.7338416634806</v>
+        <v>382.0863413931397</v>
       </c>
       <c r="C23" t="n">
-        <v>287.2728917710076</v>
+        <v>364.6253915006667</v>
       </c>
       <c r="D23" t="n">
-        <v>276.683041620683</v>
+        <v>354.0355413503421</v>
       </c>
       <c r="E23" t="n">
-        <v>303.9303700722618</v>
+        <v>381.2828698019209</v>
       </c>
       <c r="F23" t="n">
-        <v>328.8760457417114</v>
+        <v>406.2285454713706</v>
       </c>
       <c r="G23" t="n">
-        <v>337.1740942990547</v>
+        <v>414.2403485651241</v>
       </c>
       <c r="H23" t="n">
-        <v>260.1573347790837</v>
+        <v>334.5783231547555</v>
       </c>
       <c r="I23" t="n">
-        <v>127.5163719824662</v>
+        <v>193.8333934770857</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,28 +24211,28 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>63.78823351903912</v>
+        <v>123.1598666464854</v>
       </c>
       <c r="S23" t="n">
-        <v>128.0886122998132</v>
+        <v>198.9182935279234</v>
       </c>
       <c r="T23" t="n">
-        <v>144.5327138857394</v>
+        <v>220.6321740985349</v>
       </c>
       <c r="U23" t="n">
-        <v>173.3353614505501</v>
+        <v>250.664961543122</v>
       </c>
       <c r="V23" t="n">
-        <v>249.7522584701349</v>
+        <v>327.104758199794</v>
       </c>
       <c r="W23" t="n">
-        <v>271.240968717413</v>
+        <v>348.5934684470722</v>
       </c>
       <c r="X23" t="n">
-        <v>291.731100678469</v>
+        <v>369.0836004081282</v>
       </c>
       <c r="Y23" t="n">
-        <v>308.2379386560536</v>
+        <v>385.5904383857127</v>
       </c>
     </row>
     <row r="24">
@@ -24242,28 +24242,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>88.53318364986734</v>
+        <v>165.8856833795265</v>
       </c>
       <c r="C24" t="n">
-        <v>94.70849898831574</v>
+        <v>172.0609987179749</v>
       </c>
       <c r="D24" t="n">
-        <v>69.44506556463875</v>
+        <v>146.7975652942979</v>
       </c>
       <c r="E24" t="n">
-        <v>79.64508045540094</v>
+        <v>156.9975801850601</v>
       </c>
       <c r="F24" t="n">
-        <v>67.06921239338388</v>
+        <v>144.421712123043</v>
       </c>
       <c r="G24" t="n">
-        <v>59.27468697453139</v>
+        <v>136.4740318790256</v>
       </c>
       <c r="H24" t="n">
-        <v>33.57068951951533</v>
+        <v>109.4440360692917</v>
       </c>
       <c r="I24" t="n">
-        <v>9.026821530660357</v>
+        <v>81.10622749915723</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -24290,28 +24290,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>17.88432471868087</v>
+        <v>85.72779065432562</v>
       </c>
       <c r="S24" t="n">
-        <v>92.40468053780009</v>
+        <v>166.9123965631889</v>
       </c>
       <c r="T24" t="n">
-        <v>121.8872947325575</v>
+        <v>198.6224730397315</v>
       </c>
       <c r="U24" t="n">
-        <v>147.936853779088</v>
+        <v>225.2792775334074</v>
       </c>
       <c r="V24" t="n">
-        <v>154.8005871494253</v>
+        <v>232.1530868790844</v>
       </c>
       <c r="W24" t="n">
-        <v>173.6949831609196</v>
+        <v>251.0474828905787</v>
       </c>
       <c r="X24" t="n">
-        <v>127.7729852034775</v>
+        <v>205.1254849331366</v>
       </c>
       <c r="Y24" t="n">
-        <v>127.6826957773044</v>
+        <v>205.0351955069635</v>
       </c>
     </row>
     <row r="25">
@@ -24321,31 +24321,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>101.8319801819373</v>
+        <v>179.1844799115964</v>
       </c>
       <c r="C25" t="n">
-        <v>89.24682109862783</v>
+        <v>166.599320828287</v>
       </c>
       <c r="D25" t="n">
-        <v>70.61547301821236</v>
+        <v>147.9679727478715</v>
       </c>
       <c r="E25" t="n">
-        <v>68.43396264656917</v>
+        <v>145.7864623762283</v>
       </c>
       <c r="F25" t="n">
-        <v>67.42104802293125</v>
+        <v>144.7735477525904</v>
       </c>
       <c r="G25" t="n">
-        <v>89.93327444042598</v>
+        <v>167.1573743094708</v>
       </c>
       <c r="H25" t="n">
-        <v>83.71412332711171</v>
+        <v>159.9250315687638</v>
       </c>
       <c r="I25" t="n">
-        <v>75.7151306649632</v>
+        <v>149.2062964045127</v>
       </c>
       <c r="J25" t="n">
-        <v>11.27944241175474</v>
+        <v>79.5540719959837</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -24366,31 +24366,31 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.330043251694391</v>
+        <v>69.93080556209708</v>
       </c>
       <c r="R25" t="n">
-        <v>96.6987684263498</v>
+        <v>168.2779435142065</v>
       </c>
       <c r="S25" t="n">
-        <v>145.0109586927099</v>
+        <v>220.1257990333001</v>
       </c>
       <c r="T25" t="n">
-        <v>149.6990320512323</v>
+        <v>226.5029141946304</v>
       </c>
       <c r="U25" t="n">
-        <v>208.3158818155073</v>
+        <v>285.6613779164056</v>
       </c>
       <c r="V25" t="n">
-        <v>174.137643323828</v>
+        <v>251.4901430534871</v>
       </c>
       <c r="W25" t="n">
-        <v>208.522998336591</v>
+        <v>285.8754980662501</v>
       </c>
       <c r="X25" t="n">
-        <v>147.7096553890372</v>
+        <v>225.0621551186963</v>
       </c>
       <c r="Y25" t="n">
-        <v>140.5846533520948</v>
+        <v>217.9371530817539</v>
       </c>
     </row>
     <row r="26">
@@ -24400,28 +24400,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>305.7338416634806</v>
+        <v>382.0863413931397</v>
       </c>
       <c r="C26" t="n">
-        <v>288.2728917710076</v>
+        <v>364.6253915006667</v>
       </c>
       <c r="D26" t="n">
-        <v>277.683041620683</v>
+        <v>354.0355413503421</v>
       </c>
       <c r="E26" t="n">
-        <v>304.9303700722618</v>
+        <v>381.2828698019209</v>
       </c>
       <c r="F26" t="n">
-        <v>329.8760457417114</v>
+        <v>406.2285454713706</v>
       </c>
       <c r="G26" t="n">
-        <v>338.1740942990547</v>
+        <v>414.2403485651241</v>
       </c>
       <c r="H26" t="n">
-        <v>261.1573347790837</v>
+        <v>334.5783231547555</v>
       </c>
       <c r="I26" t="n">
-        <v>128.5163719824662</v>
+        <v>193.8333934770857</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,28 +24448,28 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>64.78823351903912</v>
+        <v>123.1598666464854</v>
       </c>
       <c r="S26" t="n">
-        <v>129.0886122998132</v>
+        <v>198.9182935279234</v>
       </c>
       <c r="T26" t="n">
-        <v>145.5327138857394</v>
+        <v>220.6321740985349</v>
       </c>
       <c r="U26" t="n">
-        <v>174.3353614505501</v>
+        <v>250.664961543122</v>
       </c>
       <c r="V26" t="n">
-        <v>250.7522584701349</v>
+        <v>327.104758199794</v>
       </c>
       <c r="W26" t="n">
-        <v>272.240968717413</v>
+        <v>348.5934684470722</v>
       </c>
       <c r="X26" t="n">
-        <v>292.731100678469</v>
+        <v>369.0836004081282</v>
       </c>
       <c r="Y26" t="n">
-        <v>309.2379386560536</v>
+        <v>385.5904383857127</v>
       </c>
     </row>
     <row r="27">
@@ -24479,28 +24479,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>89.53318364986734</v>
+        <v>165.8856833795265</v>
       </c>
       <c r="C27" t="n">
-        <v>95.70849898831574</v>
+        <v>172.0609987179749</v>
       </c>
       <c r="D27" t="n">
-        <v>70.44506556463875</v>
+        <v>146.7975652942979</v>
       </c>
       <c r="E27" t="n">
-        <v>80.64508045540094</v>
+        <v>156.9975801850601</v>
       </c>
       <c r="F27" t="n">
-        <v>68.06921239338388</v>
+        <v>144.421712123043</v>
       </c>
       <c r="G27" t="n">
-        <v>60.27468697453139</v>
+        <v>136.4740318790256</v>
       </c>
       <c r="H27" t="n">
-        <v>34.57068951951533</v>
+        <v>109.4440360692917</v>
       </c>
       <c r="I27" t="n">
-        <v>10.02682153066036</v>
+        <v>81.10622749915723</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,28 +24527,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>18.88432471868087</v>
+        <v>85.72779065432562</v>
       </c>
       <c r="S27" t="n">
-        <v>93.40468053780009</v>
+        <v>166.9123965631889</v>
       </c>
       <c r="T27" t="n">
-        <v>122.8872947325575</v>
+        <v>198.6224730397315</v>
       </c>
       <c r="U27" t="n">
-        <v>148.936853779088</v>
+        <v>225.2792775334074</v>
       </c>
       <c r="V27" t="n">
-        <v>155.8005871494253</v>
+        <v>232.1530868790844</v>
       </c>
       <c r="W27" t="n">
-        <v>174.6949831609196</v>
+        <v>251.0474828905787</v>
       </c>
       <c r="X27" t="n">
-        <v>128.7729852034775</v>
+        <v>205.1254849331366</v>
       </c>
       <c r="Y27" t="n">
-        <v>128.6826957773044</v>
+        <v>205.0351955069635</v>
       </c>
     </row>
     <row r="28">
@@ -24558,31 +24558,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>102.8319801819373</v>
+        <v>179.1844799115964</v>
       </c>
       <c r="C28" t="n">
-        <v>90.24682109862783</v>
+        <v>166.599320828287</v>
       </c>
       <c r="D28" t="n">
-        <v>71.61547301821236</v>
+        <v>147.9679727478715</v>
       </c>
       <c r="E28" t="n">
-        <v>69.43396264656917</v>
+        <v>145.7864623762283</v>
       </c>
       <c r="F28" t="n">
-        <v>68.42104802293125</v>
+        <v>144.7735477525904</v>
       </c>
       <c r="G28" t="n">
-        <v>90.93327444042598</v>
+        <v>167.1573743094708</v>
       </c>
       <c r="H28" t="n">
-        <v>84.71412332711171</v>
+        <v>159.9250315687638</v>
       </c>
       <c r="I28" t="n">
-        <v>76.7151306649632</v>
+        <v>149.2062964045127</v>
       </c>
       <c r="J28" t="n">
-        <v>12.27944241175474</v>
+        <v>79.5540719959837</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24603,31 +24603,31 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.330043251694391</v>
+        <v>69.93080556209708</v>
       </c>
       <c r="R28" t="n">
-        <v>97.6987684263498</v>
+        <v>168.2779435142065</v>
       </c>
       <c r="S28" t="n">
-        <v>146.0109586927099</v>
+        <v>220.1257990333001</v>
       </c>
       <c r="T28" t="n">
-        <v>150.6990320512323</v>
+        <v>226.5029141946304</v>
       </c>
       <c r="U28" t="n">
-        <v>209.3158818155073</v>
+        <v>285.6613779164056</v>
       </c>
       <c r="V28" t="n">
-        <v>175.137643323828</v>
+        <v>251.4901430534871</v>
       </c>
       <c r="W28" t="n">
-        <v>209.522998336591</v>
+        <v>285.8754980662501</v>
       </c>
       <c r="X28" t="n">
-        <v>148.7096553890372</v>
+        <v>225.0621551186963</v>
       </c>
       <c r="Y28" t="n">
-        <v>141.5846533520948</v>
+        <v>217.9371530817539</v>
       </c>
     </row>
     <row r="29">
@@ -24637,28 +24637,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>270.7338416634806</v>
+        <v>272.6423053238479</v>
       </c>
       <c r="C29" t="n">
-        <v>253.2728917710076</v>
+        <v>255.1813554313749</v>
       </c>
       <c r="D29" t="n">
-        <v>242.683041620683</v>
+        <v>244.5915052810503</v>
       </c>
       <c r="E29" t="n">
-        <v>269.9303700722618</v>
+        <v>271.8388337326292</v>
       </c>
       <c r="F29" t="n">
-        <v>294.8760457417114</v>
+        <v>296.7845094020788</v>
       </c>
       <c r="G29" t="n">
-        <v>303.1740942990547</v>
+        <v>304.7963124958324</v>
       </c>
       <c r="H29" t="n">
-        <v>226.1573347790837</v>
+        <v>225.1342870854637</v>
       </c>
       <c r="I29" t="n">
-        <v>93.51637198246621</v>
+        <v>84.38935740779392</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,28 +24685,28 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>29.78823351903912</v>
+        <v>13.71583057719366</v>
       </c>
       <c r="S29" t="n">
-        <v>94.08861229981318</v>
+        <v>89.4742574586316</v>
       </c>
       <c r="T29" t="n">
-        <v>110.5327138857394</v>
+        <v>111.1881380292431</v>
       </c>
       <c r="U29" t="n">
-        <v>139.3353614505501</v>
+        <v>141.2209254738303</v>
       </c>
       <c r="V29" t="n">
-        <v>215.7522584701349</v>
+        <v>217.6607221305023</v>
       </c>
       <c r="W29" t="n">
-        <v>237.240968717413</v>
+        <v>239.1494323777804</v>
       </c>
       <c r="X29" t="n">
-        <v>257.731100678469</v>
+        <v>259.6395643388364</v>
       </c>
       <c r="Y29" t="n">
-        <v>274.2379386560536</v>
+        <v>276.146402316421</v>
       </c>
     </row>
     <row r="30">
@@ -24716,22 +24716,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>54.53318364986734</v>
+        <v>56.44164731023473</v>
       </c>
       <c r="C30" t="n">
-        <v>60.70849898831574</v>
+        <v>62.61696264868313</v>
       </c>
       <c r="D30" t="n">
-        <v>35.44506556463875</v>
+        <v>37.35352922500614</v>
       </c>
       <c r="E30" t="n">
-        <v>45.64508045540094</v>
+        <v>47.55354411576833</v>
       </c>
       <c r="F30" t="n">
-        <v>33.06921239338388</v>
+        <v>34.97767605375127</v>
       </c>
       <c r="G30" t="n">
-        <v>25.27468697453139</v>
+        <v>27.02999580973381</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -24767,25 +24767,25 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>58.40468053780009</v>
+        <v>57.46836049389714</v>
       </c>
       <c r="T30" t="n">
-        <v>87.88729473255745</v>
+        <v>89.17843697043973</v>
       </c>
       <c r="U30" t="n">
-        <v>113.936853779088</v>
+        <v>115.8352414641156</v>
       </c>
       <c r="V30" t="n">
-        <v>120.8005871494253</v>
+        <v>122.7090508097927</v>
       </c>
       <c r="W30" t="n">
-        <v>139.6949831609196</v>
+        <v>141.603446821287</v>
       </c>
       <c r="X30" t="n">
-        <v>93.77298520347748</v>
+        <v>95.68144886384486</v>
       </c>
       <c r="Y30" t="n">
-        <v>93.68269577730436</v>
+        <v>95.59115943767175</v>
       </c>
     </row>
     <row r="31">
@@ -24795,28 +24795,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>67.8319801819373</v>
+        <v>69.74044384230469</v>
       </c>
       <c r="C31" t="n">
-        <v>55.24682109862783</v>
+        <v>57.15528475899522</v>
       </c>
       <c r="D31" t="n">
-        <v>36.61547301821236</v>
+        <v>38.52393667857974</v>
       </c>
       <c r="E31" t="n">
-        <v>34.43396264656917</v>
+        <v>36.34242630693656</v>
       </c>
       <c r="F31" t="n">
-        <v>33.42104802293125</v>
+        <v>35.32951168329863</v>
       </c>
       <c r="G31" t="n">
-        <v>55.93327444042598</v>
+        <v>57.71333824017907</v>
       </c>
       <c r="H31" t="n">
-        <v>49.71412332711171</v>
+        <v>50.48099549947206</v>
       </c>
       <c r="I31" t="n">
-        <v>41.7151306649632</v>
+        <v>39.7622603352209</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -24843,28 +24843,28 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>62.6987684263498</v>
+        <v>58.83390744491476</v>
       </c>
       <c r="S31" t="n">
-        <v>111.0109586927099</v>
+        <v>110.6817629640083</v>
       </c>
       <c r="T31" t="n">
-        <v>115.6990320512323</v>
+        <v>117.0588781253387</v>
       </c>
       <c r="U31" t="n">
-        <v>174.3158818155073</v>
+        <v>176.2173418471139</v>
       </c>
       <c r="V31" t="n">
-        <v>140.137643323828</v>
+        <v>142.0461069841954</v>
       </c>
       <c r="W31" t="n">
-        <v>174.522998336591</v>
+        <v>176.4314619969584</v>
       </c>
       <c r="X31" t="n">
-        <v>113.7096553890372</v>
+        <v>115.6181190494045</v>
       </c>
       <c r="Y31" t="n">
-        <v>106.5846533520948</v>
+        <v>108.4931170124622</v>
       </c>
     </row>
     <row r="32">
@@ -24874,28 +24874,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>270.7338416634806</v>
+        <v>272.6423053238479</v>
       </c>
       <c r="C32" t="n">
-        <v>253.2728917710076</v>
+        <v>255.1813554313749</v>
       </c>
       <c r="D32" t="n">
-        <v>242.683041620683</v>
+        <v>244.5915052810503</v>
       </c>
       <c r="E32" t="n">
-        <v>269.9303700722618</v>
+        <v>271.8388337326292</v>
       </c>
       <c r="F32" t="n">
-        <v>294.8760457417114</v>
+        <v>296.7845094020788</v>
       </c>
       <c r="G32" t="n">
-        <v>303.1740942990547</v>
+        <v>304.7963124958324</v>
       </c>
       <c r="H32" t="n">
-        <v>226.1573347790837</v>
+        <v>225.1342870854637</v>
       </c>
       <c r="I32" t="n">
-        <v>93.51637198246621</v>
+        <v>84.38935740779392</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,28 +24922,28 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>29.78823351903912</v>
+        <v>13.71583057719366</v>
       </c>
       <c r="S32" t="n">
-        <v>94.08861229981318</v>
+        <v>89.4742574586316</v>
       </c>
       <c r="T32" t="n">
-        <v>110.5327138857394</v>
+        <v>111.1881380292431</v>
       </c>
       <c r="U32" t="n">
-        <v>139.3353614505501</v>
+        <v>141.2209254738303</v>
       </c>
       <c r="V32" t="n">
-        <v>215.7522584701349</v>
+        <v>217.6607221305023</v>
       </c>
       <c r="W32" t="n">
-        <v>237.240968717413</v>
+        <v>239.1494323777804</v>
       </c>
       <c r="X32" t="n">
-        <v>257.731100678469</v>
+        <v>259.6395643388364</v>
       </c>
       <c r="Y32" t="n">
-        <v>274.2379386560536</v>
+        <v>276.146402316421</v>
       </c>
     </row>
     <row r="33">
@@ -24953,22 +24953,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>54.53318364986734</v>
+        <v>56.44164731023473</v>
       </c>
       <c r="C33" t="n">
-        <v>60.70849898831574</v>
+        <v>62.61696264868313</v>
       </c>
       <c r="D33" t="n">
-        <v>35.44506556463875</v>
+        <v>37.35352922500614</v>
       </c>
       <c r="E33" t="n">
-        <v>45.64508045540094</v>
+        <v>47.55354411576833</v>
       </c>
       <c r="F33" t="n">
-        <v>33.06921239338388</v>
+        <v>34.97767605375127</v>
       </c>
       <c r="G33" t="n">
-        <v>25.27468697453139</v>
+        <v>27.02999580973381</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -25004,25 +25004,25 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>58.40468053780009</v>
+        <v>57.46836049389714</v>
       </c>
       <c r="T33" t="n">
-        <v>87.88729473255745</v>
+        <v>89.17843697043973</v>
       </c>
       <c r="U33" t="n">
-        <v>113.936853779088</v>
+        <v>115.8352414641156</v>
       </c>
       <c r="V33" t="n">
-        <v>120.8005871494253</v>
+        <v>122.7090508097927</v>
       </c>
       <c r="W33" t="n">
-        <v>139.6949831609196</v>
+        <v>141.603446821287</v>
       </c>
       <c r="X33" t="n">
-        <v>93.77298520347748</v>
+        <v>95.68144886384486</v>
       </c>
       <c r="Y33" t="n">
-        <v>93.68269577730436</v>
+        <v>95.59115943767175</v>
       </c>
     </row>
     <row r="34">
@@ -25032,28 +25032,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>67.8319801819373</v>
+        <v>69.74044384230469</v>
       </c>
       <c r="C34" t="n">
-        <v>55.24682109862783</v>
+        <v>57.15528475899522</v>
       </c>
       <c r="D34" t="n">
-        <v>36.61547301821236</v>
+        <v>38.52393667857974</v>
       </c>
       <c r="E34" t="n">
-        <v>34.43396264656917</v>
+        <v>36.34242630693656</v>
       </c>
       <c r="F34" t="n">
-        <v>33.42104802293125</v>
+        <v>35.32951168329863</v>
       </c>
       <c r="G34" t="n">
-        <v>55.93327444042598</v>
+        <v>57.71333824017907</v>
       </c>
       <c r="H34" t="n">
-        <v>49.71412332711171</v>
+        <v>50.48099549947206</v>
       </c>
       <c r="I34" t="n">
-        <v>41.7151306649632</v>
+        <v>39.7622603352209</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -25080,28 +25080,28 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>62.6987684263498</v>
+        <v>58.83390744491476</v>
       </c>
       <c r="S34" t="n">
-        <v>111.0109586927099</v>
+        <v>110.6817629640083</v>
       </c>
       <c r="T34" t="n">
-        <v>115.6990320512323</v>
+        <v>117.0588781253387</v>
       </c>
       <c r="U34" t="n">
-        <v>174.3158818155073</v>
+        <v>176.2173418471139</v>
       </c>
       <c r="V34" t="n">
-        <v>140.137643323828</v>
+        <v>142.0461069841954</v>
       </c>
       <c r="W34" t="n">
-        <v>174.522998336591</v>
+        <v>176.4314619969584</v>
       </c>
       <c r="X34" t="n">
-        <v>113.7096553890372</v>
+        <v>115.6181190494045</v>
       </c>
       <c r="Y34" t="n">
-        <v>106.5846533520948</v>
+        <v>108.4931170124622</v>
       </c>
     </row>
     <row r="35">
@@ -25111,28 +25111,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>270.7338416634806</v>
+        <v>272.6423053238479</v>
       </c>
       <c r="C35" t="n">
-        <v>253.2728917710076</v>
+        <v>255.1813554313749</v>
       </c>
       <c r="D35" t="n">
-        <v>242.683041620683</v>
+        <v>244.5915052810503</v>
       </c>
       <c r="E35" t="n">
-        <v>269.9303700722618</v>
+        <v>271.8388337326292</v>
       </c>
       <c r="F35" t="n">
-        <v>294.8760457417114</v>
+        <v>296.7845094020788</v>
       </c>
       <c r="G35" t="n">
-        <v>303.1740942990547</v>
+        <v>304.7963124958324</v>
       </c>
       <c r="H35" t="n">
-        <v>226.1573347790837</v>
+        <v>225.1342870854637</v>
       </c>
       <c r="I35" t="n">
-        <v>93.51637198246621</v>
+        <v>84.38935740779392</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,28 +25159,28 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>29.78823351903912</v>
+        <v>13.71583057719366</v>
       </c>
       <c r="S35" t="n">
-        <v>94.08861229981318</v>
+        <v>89.4742574586316</v>
       </c>
       <c r="T35" t="n">
-        <v>110.5327138857394</v>
+        <v>111.1881380292431</v>
       </c>
       <c r="U35" t="n">
-        <v>139.3353614505501</v>
+        <v>141.2209254738303</v>
       </c>
       <c r="V35" t="n">
-        <v>215.7522584701349</v>
+        <v>217.6607221305023</v>
       </c>
       <c r="W35" t="n">
-        <v>237.240968717413</v>
+        <v>239.1494323777804</v>
       </c>
       <c r="X35" t="n">
-        <v>257.731100678469</v>
+        <v>259.6395643388364</v>
       </c>
       <c r="Y35" t="n">
-        <v>274.2379386560536</v>
+        <v>276.146402316421</v>
       </c>
     </row>
     <row r="36">
@@ -25190,22 +25190,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>54.53318364986734</v>
+        <v>56.44164731023473</v>
       </c>
       <c r="C36" t="n">
-        <v>60.70849898831574</v>
+        <v>62.61696264868313</v>
       </c>
       <c r="D36" t="n">
-        <v>35.44506556463875</v>
+        <v>37.35352922500614</v>
       </c>
       <c r="E36" t="n">
-        <v>45.64508045540094</v>
+        <v>47.55354411576833</v>
       </c>
       <c r="F36" t="n">
-        <v>33.06921239338388</v>
+        <v>34.97767605375127</v>
       </c>
       <c r="G36" t="n">
-        <v>25.27468697453139</v>
+        <v>27.02999580973381</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -25241,25 +25241,25 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>58.40468053780009</v>
+        <v>57.46836049389714</v>
       </c>
       <c r="T36" t="n">
-        <v>87.88729473255745</v>
+        <v>89.17843697043973</v>
       </c>
       <c r="U36" t="n">
-        <v>113.936853779088</v>
+        <v>115.8352414641156</v>
       </c>
       <c r="V36" t="n">
-        <v>120.8005871494253</v>
+        <v>122.7090508097927</v>
       </c>
       <c r="W36" t="n">
-        <v>139.6949831609196</v>
+        <v>141.603446821287</v>
       </c>
       <c r="X36" t="n">
-        <v>93.77298520347748</v>
+        <v>95.68144886384486</v>
       </c>
       <c r="Y36" t="n">
-        <v>93.68269577730436</v>
+        <v>95.59115943767175</v>
       </c>
     </row>
     <row r="37">
@@ -25269,28 +25269,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>67.8319801819373</v>
+        <v>69.74044384230469</v>
       </c>
       <c r="C37" t="n">
-        <v>55.24682109862783</v>
+        <v>57.15528475899522</v>
       </c>
       <c r="D37" t="n">
-        <v>36.61547301821236</v>
+        <v>38.52393667857974</v>
       </c>
       <c r="E37" t="n">
-        <v>34.43396264656917</v>
+        <v>36.34242630693656</v>
       </c>
       <c r="F37" t="n">
-        <v>33.42104802293125</v>
+        <v>35.32951168329863</v>
       </c>
       <c r="G37" t="n">
-        <v>55.93327444042598</v>
+        <v>57.71333824017907</v>
       </c>
       <c r="H37" t="n">
-        <v>49.71412332711171</v>
+        <v>50.48099549947206</v>
       </c>
       <c r="I37" t="n">
-        <v>41.7151306649632</v>
+        <v>39.7622603352209</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -25317,28 +25317,28 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>62.6987684263498</v>
+        <v>58.83390744491476</v>
       </c>
       <c r="S37" t="n">
-        <v>111.0109586927099</v>
+        <v>110.6817629640083</v>
       </c>
       <c r="T37" t="n">
-        <v>115.6990320512323</v>
+        <v>117.0588781253387</v>
       </c>
       <c r="U37" t="n">
-        <v>174.3158818155073</v>
+        <v>176.2173418471139</v>
       </c>
       <c r="V37" t="n">
-        <v>140.137643323828</v>
+        <v>142.0461069841954</v>
       </c>
       <c r="W37" t="n">
-        <v>174.522998336591</v>
+        <v>176.4314619969584</v>
       </c>
       <c r="X37" t="n">
-        <v>113.7096553890372</v>
+        <v>115.6181190494045</v>
       </c>
       <c r="Y37" t="n">
-        <v>106.5846533520948</v>
+        <v>108.4931170124622</v>
       </c>
     </row>
     <row r="38">
@@ -25348,28 +25348,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>270.7338416634806</v>
+        <v>272.6423053238479</v>
       </c>
       <c r="C38" t="n">
-        <v>253.2728917710076</v>
+        <v>255.1813554313749</v>
       </c>
       <c r="D38" t="n">
-        <v>242.683041620683</v>
+        <v>244.5915052810503</v>
       </c>
       <c r="E38" t="n">
-        <v>269.9303700722618</v>
+        <v>271.8388337326292</v>
       </c>
       <c r="F38" t="n">
-        <v>294.8760457417114</v>
+        <v>296.7845094020788</v>
       </c>
       <c r="G38" t="n">
-        <v>303.1740942990547</v>
+        <v>304.7963124958324</v>
       </c>
       <c r="H38" t="n">
-        <v>226.1573347790837</v>
+        <v>225.1342870854637</v>
       </c>
       <c r="I38" t="n">
-        <v>93.51637198246621</v>
+        <v>84.38935740779392</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,28 +25396,28 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>29.78823351903912</v>
+        <v>13.71583057719366</v>
       </c>
       <c r="S38" t="n">
-        <v>94.08861229981318</v>
+        <v>89.4742574586316</v>
       </c>
       <c r="T38" t="n">
-        <v>110.5327138857394</v>
+        <v>111.1881380292431</v>
       </c>
       <c r="U38" t="n">
-        <v>139.3353614505501</v>
+        <v>141.2209254738303</v>
       </c>
       <c r="V38" t="n">
-        <v>215.7522584701349</v>
+        <v>217.6607221305023</v>
       </c>
       <c r="W38" t="n">
-        <v>237.240968717413</v>
+        <v>239.1494323777804</v>
       </c>
       <c r="X38" t="n">
-        <v>257.731100678469</v>
+        <v>259.6395643388364</v>
       </c>
       <c r="Y38" t="n">
-        <v>274.2379386560536</v>
+        <v>276.146402316421</v>
       </c>
     </row>
     <row r="39">
@@ -25427,22 +25427,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>54.53318364986734</v>
+        <v>56.44164731023473</v>
       </c>
       <c r="C39" t="n">
-        <v>60.70849898831574</v>
+        <v>62.61696264868313</v>
       </c>
       <c r="D39" t="n">
-        <v>35.44506556463875</v>
+        <v>37.35352922500614</v>
       </c>
       <c r="E39" t="n">
-        <v>45.64508045540094</v>
+        <v>47.55354411576833</v>
       </c>
       <c r="F39" t="n">
-        <v>33.06921239338388</v>
+        <v>34.97767605375127</v>
       </c>
       <c r="G39" t="n">
-        <v>25.27468697453139</v>
+        <v>27.02999580973381</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -25478,25 +25478,25 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>58.40468053780009</v>
+        <v>57.46836049389714</v>
       </c>
       <c r="T39" t="n">
-        <v>87.88729473255745</v>
+        <v>89.17843697043973</v>
       </c>
       <c r="U39" t="n">
-        <v>113.936853779088</v>
+        <v>115.8352414641156</v>
       </c>
       <c r="V39" t="n">
-        <v>120.8005871494253</v>
+        <v>122.7090508097927</v>
       </c>
       <c r="W39" t="n">
-        <v>139.6949831609196</v>
+        <v>141.603446821287</v>
       </c>
       <c r="X39" t="n">
-        <v>93.77298520347748</v>
+        <v>95.68144886384486</v>
       </c>
       <c r="Y39" t="n">
-        <v>93.68269577730436</v>
+        <v>95.59115943767175</v>
       </c>
     </row>
     <row r="40">
@@ -25506,28 +25506,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>67.8319801819373</v>
+        <v>69.74044384230469</v>
       </c>
       <c r="C40" t="n">
-        <v>55.24682109862783</v>
+        <v>57.15528475899522</v>
       </c>
       <c r="D40" t="n">
-        <v>36.61547301821236</v>
+        <v>38.52393667857974</v>
       </c>
       <c r="E40" t="n">
-        <v>34.43396264656917</v>
+        <v>36.34242630693656</v>
       </c>
       <c r="F40" t="n">
-        <v>33.42104802293125</v>
+        <v>35.32951168329863</v>
       </c>
       <c r="G40" t="n">
-        <v>55.93327444042598</v>
+        <v>57.71333824017907</v>
       </c>
       <c r="H40" t="n">
-        <v>49.71412332711171</v>
+        <v>50.48099549947206</v>
       </c>
       <c r="I40" t="n">
-        <v>41.7151306649632</v>
+        <v>39.7622603352209</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -25554,28 +25554,28 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>62.6987684263498</v>
+        <v>58.83390744491476</v>
       </c>
       <c r="S40" t="n">
-        <v>111.0109586927099</v>
+        <v>110.6817629640083</v>
       </c>
       <c r="T40" t="n">
-        <v>115.6990320512323</v>
+        <v>117.0588781253387</v>
       </c>
       <c r="U40" t="n">
-        <v>174.3158818155073</v>
+        <v>176.2173418471139</v>
       </c>
       <c r="V40" t="n">
-        <v>140.137643323828</v>
+        <v>142.0461069841954</v>
       </c>
       <c r="W40" t="n">
-        <v>174.522998336591</v>
+        <v>176.4314619969584</v>
       </c>
       <c r="X40" t="n">
-        <v>113.7096553890372</v>
+        <v>115.6181190494045</v>
       </c>
       <c r="Y40" t="n">
-        <v>106.5846533520948</v>
+        <v>108.4931170124622</v>
       </c>
     </row>
     <row r="41">
@@ -25585,28 +25585,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>270.7338416634806</v>
+        <v>272.6423053238479</v>
       </c>
       <c r="C41" t="n">
-        <v>253.2728917710076</v>
+        <v>255.1813554313749</v>
       </c>
       <c r="D41" t="n">
-        <v>242.683041620683</v>
+        <v>244.5915052810503</v>
       </c>
       <c r="E41" t="n">
-        <v>269.9303700722618</v>
+        <v>271.8388337326292</v>
       </c>
       <c r="F41" t="n">
-        <v>294.8760457417114</v>
+        <v>296.7845094020788</v>
       </c>
       <c r="G41" t="n">
-        <v>303.1740942990547</v>
+        <v>304.7963124958324</v>
       </c>
       <c r="H41" t="n">
-        <v>226.1573347790837</v>
+        <v>225.1342870854637</v>
       </c>
       <c r="I41" t="n">
-        <v>93.51637198246621</v>
+        <v>84.38935740779392</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,28 +25633,28 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>29.78823351903913</v>
+        <v>13.71583057719366</v>
       </c>
       <c r="S41" t="n">
-        <v>94.08861229981318</v>
+        <v>89.4742574586316</v>
       </c>
       <c r="T41" t="n">
-        <v>110.5327138857394</v>
+        <v>111.1881380292431</v>
       </c>
       <c r="U41" t="n">
-        <v>139.3353614505501</v>
+        <v>141.2209254738303</v>
       </c>
       <c r="V41" t="n">
-        <v>215.7522584701349</v>
+        <v>217.6607221305023</v>
       </c>
       <c r="W41" t="n">
-        <v>237.240968717413</v>
+        <v>239.1494323777804</v>
       </c>
       <c r="X41" t="n">
-        <v>257.731100678469</v>
+        <v>259.6395643388364</v>
       </c>
       <c r="Y41" t="n">
-        <v>274.2379386560536</v>
+        <v>276.146402316421</v>
       </c>
     </row>
     <row r="42">
@@ -25664,22 +25664,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>54.53318364986734</v>
+        <v>56.44164731023473</v>
       </c>
       <c r="C42" t="n">
-        <v>60.70849898831574</v>
+        <v>62.61696264868313</v>
       </c>
       <c r="D42" t="n">
-        <v>35.44506556463875</v>
+        <v>37.35352922500614</v>
       </c>
       <c r="E42" t="n">
-        <v>45.64508045540094</v>
+        <v>47.55354411576833</v>
       </c>
       <c r="F42" t="n">
-        <v>33.06921239338388</v>
+        <v>34.97767605375127</v>
       </c>
       <c r="G42" t="n">
-        <v>25.27468697453139</v>
+        <v>27.02999580973381</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -25715,25 +25715,25 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>58.40468053780009</v>
+        <v>57.46836049389714</v>
       </c>
       <c r="T42" t="n">
-        <v>87.88729473255745</v>
+        <v>89.17843697043973</v>
       </c>
       <c r="U42" t="n">
-        <v>113.936853779088</v>
+        <v>115.8352414641156</v>
       </c>
       <c r="V42" t="n">
-        <v>120.8005871494253</v>
+        <v>122.7090508097927</v>
       </c>
       <c r="W42" t="n">
-        <v>139.6949831609196</v>
+        <v>141.603446821287</v>
       </c>
       <c r="X42" t="n">
-        <v>93.77298520347748</v>
+        <v>95.68144886384486</v>
       </c>
       <c r="Y42" t="n">
-        <v>93.68269577730436</v>
+        <v>95.59115943767175</v>
       </c>
     </row>
     <row r="43">
@@ -25743,28 +25743,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>67.8319801819373</v>
+        <v>69.74044384230469</v>
       </c>
       <c r="C43" t="n">
-        <v>55.24682109862783</v>
+        <v>57.15528475899522</v>
       </c>
       <c r="D43" t="n">
-        <v>36.61547301821236</v>
+        <v>38.52393667857974</v>
       </c>
       <c r="E43" t="n">
-        <v>34.43396264656917</v>
+        <v>36.34242630693656</v>
       </c>
       <c r="F43" t="n">
-        <v>33.42104802293125</v>
+        <v>35.32951168329863</v>
       </c>
       <c r="G43" t="n">
-        <v>55.93327444042598</v>
+        <v>57.71333824017907</v>
       </c>
       <c r="H43" t="n">
-        <v>49.71412332711171</v>
+        <v>50.48099549947206</v>
       </c>
       <c r="I43" t="n">
-        <v>41.7151306649632</v>
+        <v>39.7622603352209</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -25791,28 +25791,28 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>62.69876842634982</v>
+        <v>58.83390744491476</v>
       </c>
       <c r="S43" t="n">
-        <v>111.01095869271</v>
+        <v>110.6817629640083</v>
       </c>
       <c r="T43" t="n">
-        <v>115.6990320512323</v>
+        <v>117.0588781253387</v>
       </c>
       <c r="U43" t="n">
-        <v>174.3158818155073</v>
+        <v>176.2173418471139</v>
       </c>
       <c r="V43" t="n">
-        <v>140.137643323828</v>
+        <v>142.0461069841954</v>
       </c>
       <c r="W43" t="n">
-        <v>174.522998336591</v>
+        <v>176.4314619969584</v>
       </c>
       <c r="X43" t="n">
-        <v>113.7096553890372</v>
+        <v>115.6181190494045</v>
       </c>
       <c r="Y43" t="n">
-        <v>106.5846533520948</v>
+        <v>108.4931170124622</v>
       </c>
     </row>
     <row r="44">
@@ -25837,16 +25837,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>415.1740942990547</v>
+        <v>414.887848835465</v>
       </c>
       <c r="H44" t="n">
-        <v>338.1573347790837</v>
+        <v>335.2258234250963</v>
       </c>
       <c r="I44" t="n">
-        <v>205.5163719824662</v>
+        <v>194.4808937474265</v>
       </c>
       <c r="J44" t="n">
-        <v>1.030857193808496</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -25870,16 +25870,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>141.7882335190391</v>
+        <v>123.8073669168263</v>
       </c>
       <c r="S44" t="n">
-        <v>206.0886122998132</v>
+        <v>199.5657937982642</v>
       </c>
       <c r="T44" t="n">
-        <v>222.5327138857394</v>
+        <v>221.2796743688757</v>
       </c>
       <c r="U44" t="n">
-        <v>251.3353614505501</v>
+        <v>251.3124618134629</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,13 +25916,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>137.2746869745314</v>
+        <v>137.1215321493664</v>
       </c>
       <c r="H45" t="n">
-        <v>111.5706895195153</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="I45" t="n">
-        <v>87.02682153066036</v>
+        <v>81.7537277694981</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25949,16 +25949,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>95.88432471868087</v>
+        <v>86.37529092466649</v>
       </c>
       <c r="S45" t="n">
-        <v>170.4046805378001</v>
+        <v>167.5598968335298</v>
       </c>
       <c r="T45" t="n">
-        <v>199.8872947325575</v>
+        <v>199.2699733100723</v>
       </c>
       <c r="U45" t="n">
-        <v>225.936853779088</v>
+        <v>225.9267778037482</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,19 +25995,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.933274440426</v>
+        <v>167.8048745798117</v>
       </c>
       <c r="H46" t="n">
-        <v>161.7141233271117</v>
+        <v>160.5725318391047</v>
       </c>
       <c r="I46" t="n">
-        <v>153.7151306649632</v>
+        <v>149.8537966748535</v>
       </c>
       <c r="J46" t="n">
-        <v>89.27944241175474</v>
+        <v>80.20157226632458</v>
       </c>
       <c r="K46" t="n">
-        <v>15.56522953080089</v>
+        <v>0.6475002703408634</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -26025,19 +26025,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>81.33004325169439</v>
+        <v>70.57830583243795</v>
       </c>
       <c r="R46" t="n">
-        <v>174.6987684263498</v>
+        <v>168.9254437845474</v>
       </c>
       <c r="S46" t="n">
-        <v>223.0109586927099</v>
+        <v>220.773299303641</v>
       </c>
       <c r="T46" t="n">
-        <v>227.6990320512323</v>
+        <v>227.1504144649713</v>
       </c>
       <c r="U46" t="n">
-        <v>286.3158818155073</v>
+        <v>286.3088781867465</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>309194.6052558738</v>
+        <v>290676.4574396686</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>474722.6248231035</v>
+        <v>292079.7200255513</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>474722.6248231035</v>
+        <v>292079.7200255513</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>474722.6248231035</v>
+        <v>292079.7200255513</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>474722.6248231035</v>
+        <v>292079.7200255513</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>472577.0248231036</v>
+        <v>292079.7200255513</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>544935.4565663738</v>
+        <v>523417.3521128137</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>544935.4565663738</v>
+        <v>523417.3521128137</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>544935.4565663738</v>
+        <v>523417.3521128137</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>544935.4565663738</v>
+        <v>523417.3521128137</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>544935.4565663738</v>
+        <v>523417.3521128137</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>306955.7652558737</v>
+        <v>290676.4574396686</v>
       </c>
     </row>
   </sheetData>
@@ -26264,46 +26264,46 @@
         <v>696384.8879094827</v>
       </c>
       <c r="C2" t="n">
-        <v>696384.8879094826</v>
+        <v>696384.8879094827</v>
       </c>
       <c r="D2" t="n">
         <v>696384.8879094828</v>
       </c>
       <c r="E2" t="n">
-        <v>188357.7362324144</v>
+        <v>190726.6444107537</v>
       </c>
       <c r="F2" t="n">
-        <v>344689.754712576</v>
+        <v>192051.9479640873</v>
       </c>
       <c r="G2" t="n">
-        <v>344689.754712576</v>
+        <v>192051.9479640873</v>
       </c>
       <c r="H2" t="n">
-        <v>344689.7547125759</v>
+        <v>192051.9479640873</v>
       </c>
       <c r="I2" t="n">
-        <v>344689.754712576</v>
+        <v>192051.9479640873</v>
       </c>
       <c r="J2" t="n">
-        <v>342663.3547125757</v>
+        <v>192051.9479640873</v>
       </c>
       <c r="K2" t="n">
-        <v>411001.8735812198</v>
+        <v>410537.489379835</v>
       </c>
       <c r="L2" t="n">
-        <v>411001.8735812193</v>
+        <v>410537.489379835</v>
       </c>
       <c r="M2" t="n">
-        <v>411001.8735812193</v>
+        <v>410537.489379835</v>
       </c>
       <c r="N2" t="n">
-        <v>411001.8735812193</v>
+        <v>410537.489379835</v>
       </c>
       <c r="O2" t="n">
-        <v>411001.8735812199</v>
+        <v>410537.489379835</v>
       </c>
       <c r="P2" t="n">
-        <v>186243.2762324145</v>
+        <v>190726.6444107537</v>
       </c>
     </row>
     <row r="3">
@@ -26322,10 +26322,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>26508.896</v>
+        <v>82914.0489658469</v>
       </c>
       <c r="F3" t="n">
-        <v>61600</v>
+        <v>518.0002162726921</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -26340,7 +26340,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>89600</v>
+        <v>88073.22907170608</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>463150.7311021098</v>
+        <v>463844.3331297129</v>
       </c>
       <c r="C4" t="n">
-        <v>463150.7311021098</v>
+        <v>463844.333129713</v>
       </c>
       <c r="D4" t="n">
-        <v>463150.7311021098</v>
+        <v>463844.3331297129</v>
       </c>
       <c r="E4" t="n">
-        <v>111176.8423634419</v>
+        <v>89251.01711914764</v>
       </c>
       <c r="F4" t="n">
-        <v>216152.335311198</v>
+        <v>90140.94609959045</v>
       </c>
       <c r="G4" t="n">
-        <v>216152.335311198</v>
+        <v>90140.94609959045</v>
       </c>
       <c r="H4" t="n">
-        <v>216152.335311198</v>
+        <v>90140.94609959045</v>
       </c>
       <c r="I4" t="n">
-        <v>216152.335311198</v>
+        <v>90140.94609959045</v>
       </c>
       <c r="J4" t="n">
-        <v>214791.6266030435</v>
+        <v>90140.94609959045</v>
       </c>
       <c r="K4" t="n">
-        <v>260680.3049128281</v>
+        <v>236851.95024994</v>
       </c>
       <c r="L4" t="n">
-        <v>260680.3049128281</v>
+        <v>236851.95024994</v>
       </c>
       <c r="M4" t="n">
-        <v>260680.3049128281</v>
+        <v>236851.95024994</v>
       </c>
       <c r="N4" t="n">
-        <v>260680.3049128281</v>
+        <v>236851.95024994</v>
       </c>
       <c r="O4" t="n">
-        <v>260680.3049128281</v>
+        <v>236851.95024994</v>
       </c>
       <c r="P4" t="n">
-        <v>109757.0021862585</v>
+        <v>89251.01711914764</v>
       </c>
     </row>
     <row r="5">
@@ -26426,40 +26426,40 @@
         <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>781.669</v>
+        <v>2249.837587680731</v>
       </c>
       <c r="F5" t="n">
-        <v>7254.982000000001</v>
+        <v>2304.272287908017</v>
       </c>
       <c r="G5" t="n">
-        <v>7254.982000000001</v>
+        <v>2304.272287908017</v>
       </c>
       <c r="H5" t="n">
-        <v>7254.982000000001</v>
+        <v>2304.272287908017</v>
       </c>
       <c r="I5" t="n">
-        <v>7254.982000000001</v>
+        <v>2304.272287908017</v>
       </c>
       <c r="J5" t="n">
-        <v>7170.913</v>
+        <v>2304.272287908017</v>
       </c>
       <c r="K5" t="n">
-        <v>10113.328</v>
+        <v>11505.1229562173</v>
       </c>
       <c r="L5" t="n">
-        <v>10113.328</v>
+        <v>11505.1229562173</v>
       </c>
       <c r="M5" t="n">
-        <v>10113.328</v>
+        <v>11505.1229562173</v>
       </c>
       <c r="N5" t="n">
-        <v>10113.328</v>
+        <v>11505.1229562173</v>
       </c>
       <c r="O5" t="n">
-        <v>10113.328</v>
+        <v>11505.1229562173</v>
       </c>
       <c r="P5" t="n">
-        <v>697.6</v>
+        <v>2249.837587680731</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>199606.5568073729</v>
+        <v>198912.9547797698</v>
       </c>
       <c r="C6" t="n">
-        <v>199606.5568073728</v>
+        <v>198912.9547797697</v>
       </c>
       <c r="D6" t="n">
-        <v>199606.556807373</v>
+        <v>198912.9547797699</v>
       </c>
       <c r="E6" t="n">
-        <v>49890.32886897252</v>
+        <v>16311.74073807838</v>
       </c>
       <c r="F6" t="n">
-        <v>59682.43740137796</v>
+        <v>99088.72936031618</v>
       </c>
       <c r="G6" t="n">
-        <v>121282.437401378</v>
+        <v>99606.72957658887</v>
       </c>
       <c r="H6" t="n">
-        <v>121282.4374013779</v>
+        <v>99606.72957658887</v>
       </c>
       <c r="I6" t="n">
-        <v>121282.437401378</v>
+        <v>99606.72957658887</v>
       </c>
       <c r="J6" t="n">
-        <v>120700.8151095322</v>
+        <v>99606.72957658887</v>
       </c>
       <c r="K6" t="n">
-        <v>50608.24066839161</v>
+        <v>74107.18710197161</v>
       </c>
       <c r="L6" t="n">
-        <v>140208.2406683912</v>
+        <v>162180.4161736776</v>
       </c>
       <c r="M6" t="n">
-        <v>140208.2406683912</v>
+        <v>162180.4161736777</v>
       </c>
       <c r="N6" t="n">
-        <v>140208.2406683912</v>
+        <v>162180.4161736776</v>
       </c>
       <c r="O6" t="n">
-        <v>140208.2406683918</v>
+        <v>162180.4161736777</v>
       </c>
       <c r="P6" t="n">
-        <v>75788.67404615597</v>
+        <v>99225.78970392529</v>
       </c>
     </row>
   </sheetData>
@@ -26632,37 +26632,37 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="G2" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="H2" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="I2" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="J2" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="K2" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="L2" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="M2" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="N2" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="O2" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -26684,40 +26684,40 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>103.2035590679235</v>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>103.2035590679235</v>
       </c>
       <c r="G3" t="n">
-        <v>32</v>
+        <v>103.2035590679235</v>
       </c>
       <c r="H3" t="n">
-        <v>32</v>
+        <v>103.2035590679235</v>
       </c>
       <c r="I3" t="n">
-        <v>32</v>
+        <v>103.2035590679235</v>
       </c>
       <c r="J3" t="n">
-        <v>32</v>
+        <v>103.2035590679235</v>
       </c>
       <c r="K3" t="n">
-        <v>32</v>
+        <v>103.2035590679235</v>
       </c>
       <c r="L3" t="n">
-        <v>32</v>
+        <v>103.2035590679235</v>
       </c>
       <c r="M3" t="n">
-        <v>32</v>
+        <v>103.2035590679235</v>
       </c>
       <c r="N3" t="n">
-        <v>32</v>
+        <v>103.2035590679235</v>
       </c>
       <c r="O3" t="n">
-        <v>32</v>
+        <v>103.2035590679235</v>
       </c>
       <c r="P3" t="n">
-        <v>32</v>
+        <v>103.2035590679235</v>
       </c>
     </row>
     <row r="4">
@@ -26840,7 +26840,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -26849,40 +26849,40 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,49 +26892,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>103.2035590679235</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26947,7 +26947,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -26956,37 +26956,37 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27081,10 +27081,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -27099,7 +27099,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
     </row>
     <row r="3">
@@ -28012,31 +28012,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -28060,28 +28060,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -28091,28 +28091,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28139,28 +28139,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -28170,34 +28170,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -28215,31 +28215,31 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -28249,31 +28249,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="E14" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="F14" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="G14" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="H14" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="I14" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="J14" t="n">
-        <v>1.030857193808496</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -28297,28 +28297,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="S14" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="T14" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="U14" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="V14" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="W14" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="X14" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="Y14" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
     </row>
     <row r="15">
@@ -28328,28 +28328,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="C15" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="E15" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="F15" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="G15" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="H15" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="I15" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28376,28 +28376,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="S15" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="T15" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="U15" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="V15" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="W15" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="X15" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="Y15" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
     </row>
     <row r="16">
@@ -28407,34 +28407,34 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="C16" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="D16" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="E16" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="F16" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="G16" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="H16" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="I16" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="J16" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="K16" t="n">
-        <v>15.56522953080089</v>
+        <v>0.6475002703408634</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -28452,31 +28452,31 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="R16" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="S16" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="T16" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="U16" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="V16" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="W16" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="X16" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="Y16" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
     </row>
     <row r="17">
@@ -28486,31 +28486,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="C17" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="E17" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="F17" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="G17" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="H17" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="I17" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="J17" t="n">
-        <v>1.030857193808496</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -28534,28 +28534,28 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="S17" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="T17" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="U17" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="V17" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="W17" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="X17" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="Y17" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
     </row>
     <row r="18">
@@ -28565,28 +28565,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="C18" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="D18" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="E18" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="F18" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="G18" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="H18" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="I18" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28613,28 +28613,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="S18" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="T18" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="U18" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="V18" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="W18" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="X18" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="Y18" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
     </row>
     <row r="19">
@@ -28644,34 +28644,34 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="C19" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="D19" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="E19" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="F19" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="G19" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="H19" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="I19" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="J19" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="K19" t="n">
-        <v>15.56522953080089</v>
+        <v>0.6475002703408634</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -28689,31 +28689,31 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="R19" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="S19" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="T19" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="U19" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="V19" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="W19" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="X19" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="Y19" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
     </row>
     <row r="20">
@@ -28723,31 +28723,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="C20" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="D20" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="E20" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="F20" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="G20" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="H20" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="I20" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="J20" t="n">
-        <v>1.030857193808496</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -28771,28 +28771,28 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="S20" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="T20" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="U20" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="V20" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="W20" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="X20" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="Y20" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
     </row>
     <row r="21">
@@ -28802,28 +28802,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="C21" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="D21" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="E21" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="F21" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="G21" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="H21" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="I21" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -28850,28 +28850,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="S21" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="T21" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="U21" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="V21" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="W21" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="X21" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="Y21" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
     </row>
     <row r="22">
@@ -28881,34 +28881,34 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="C22" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="D22" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="E22" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="F22" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="G22" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="H22" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="I22" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="J22" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="K22" t="n">
-        <v>15.56522953080089</v>
+        <v>0.6475002703408634</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -28926,31 +28926,31 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="R22" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="S22" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="T22" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="U22" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="V22" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="W22" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="X22" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="Y22" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
     </row>
     <row r="23">
@@ -28960,31 +28960,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="C23" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="D23" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="E23" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="F23" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="G23" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="H23" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="I23" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="J23" t="n">
-        <v>1.030857193808496</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -29008,28 +29008,28 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="S23" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="T23" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="U23" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="V23" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="W23" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="X23" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="Y23" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
     </row>
     <row r="24">
@@ -29039,28 +29039,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="C24" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="D24" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="E24" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="F24" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="G24" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="H24" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="I24" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -29087,28 +29087,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="S24" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="T24" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="U24" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="V24" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="W24" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="X24" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="Y24" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
     </row>
     <row r="25">
@@ -29118,34 +29118,34 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="C25" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="D25" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="E25" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="F25" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="G25" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="H25" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="I25" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="J25" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="K25" t="n">
-        <v>15.56522953080089</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -29163,31 +29163,31 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="R25" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="S25" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="T25" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="U25" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="V25" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="W25" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="X25" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="Y25" t="n">
-        <v>78</v>
+        <v>0.6475002703408652</v>
       </c>
     </row>
     <row r="26">
@@ -29197,31 +29197,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="C26" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="D26" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="E26" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="F26" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="G26" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="H26" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="I26" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="J26" t="n">
-        <v>1.030857193808496</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -29245,28 +29245,28 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="S26" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="T26" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="U26" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="V26" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="W26" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="X26" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="Y26" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
     </row>
     <row r="27">
@@ -29276,28 +29276,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="C27" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="D27" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="E27" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="F27" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="G27" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="H27" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="I27" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29324,28 +29324,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="S27" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="T27" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="U27" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="V27" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="W27" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="X27" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="Y27" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
     </row>
     <row r="28">
@@ -29355,34 +29355,34 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="C28" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="D28" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="E28" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="F28" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="G28" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="H28" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="I28" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="J28" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="K28" t="n">
-        <v>15.56522953080089</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -29400,31 +29400,31 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="R28" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="S28" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="T28" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="U28" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="V28" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="W28" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="X28" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
       <c r="Y28" t="n">
-        <v>77</v>
+        <v>0.6475002703408652</v>
       </c>
     </row>
     <row r="29">
@@ -29434,31 +29434,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="C29" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="D29" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="E29" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="F29" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="G29" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="H29" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="I29" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="J29" t="n">
-        <v>1.030857193808496</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -29482,28 +29482,28 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="S29" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="T29" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="U29" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="V29" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="W29" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="X29" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="Y29" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
     </row>
     <row r="30">
@@ -29513,28 +29513,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="C30" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="D30" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="E30" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="F30" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="G30" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="H30" t="n">
-        <v>111.5706895195153</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="I30" t="n">
-        <v>87.02682153066036</v>
+        <v>81.7537277694981</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29561,28 +29561,28 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>95.88432471868087</v>
+        <v>86.37529092466649</v>
       </c>
       <c r="S30" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="T30" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="U30" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="V30" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="W30" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="X30" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="Y30" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
     </row>
     <row r="31">
@@ -29592,34 +29592,34 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="C31" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="D31" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="E31" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="F31" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="G31" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="H31" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="I31" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="J31" t="n">
-        <v>89.27944241175474</v>
+        <v>80.20157226632458</v>
       </c>
       <c r="K31" t="n">
-        <v>15.56522953080089</v>
+        <v>0.6475002703408634</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -29637,31 +29637,31 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>81.33004325169439</v>
+        <v>70.57830583243795</v>
       </c>
       <c r="R31" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="S31" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="T31" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="U31" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="V31" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="W31" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="X31" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="Y31" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
     </row>
     <row r="32">
@@ -29671,31 +29671,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="C32" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="D32" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="E32" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="F32" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="G32" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="H32" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="I32" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="J32" t="n">
-        <v>1.030857193808496</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -29719,28 +29719,28 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="S32" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="T32" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="U32" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="V32" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="W32" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="X32" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="Y32" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
     </row>
     <row r="33">
@@ -29750,28 +29750,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="C33" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="D33" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="E33" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="F33" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="G33" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="H33" t="n">
-        <v>111.5706895195153</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="I33" t="n">
-        <v>87.02682153066036</v>
+        <v>81.7537277694981</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29798,28 +29798,28 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>95.88432471868087</v>
+        <v>86.37529092466649</v>
       </c>
       <c r="S33" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="T33" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="U33" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="V33" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="W33" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="X33" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="Y33" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
     </row>
     <row r="34">
@@ -29829,34 +29829,34 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="C34" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="D34" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="E34" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="F34" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="G34" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="H34" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="I34" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="J34" t="n">
-        <v>89.27944241175474</v>
+        <v>80.20157226632458</v>
       </c>
       <c r="K34" t="n">
-        <v>15.56522953080089</v>
+        <v>0.6475002703408634</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -29874,31 +29874,31 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>81.33004325169439</v>
+        <v>70.57830583243795</v>
       </c>
       <c r="R34" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="S34" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="T34" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="U34" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="V34" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="W34" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="X34" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="Y34" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
     </row>
     <row r="35">
@@ -29908,31 +29908,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="C35" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="D35" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="E35" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="F35" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="G35" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="H35" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="I35" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="J35" t="n">
-        <v>1.030857193808496</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -29956,28 +29956,28 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="S35" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="T35" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="U35" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="V35" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="W35" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="X35" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="Y35" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
     </row>
     <row r="36">
@@ -29987,28 +29987,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="C36" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="D36" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="E36" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="F36" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="G36" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="H36" t="n">
-        <v>111.5706895195153</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="I36" t="n">
-        <v>87.02682153066036</v>
+        <v>81.7537277694981</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30035,28 +30035,28 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>95.88432471868087</v>
+        <v>86.37529092466649</v>
       </c>
       <c r="S36" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="T36" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="U36" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="V36" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="W36" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="X36" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="Y36" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
     </row>
     <row r="37">
@@ -30066,34 +30066,34 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="C37" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="D37" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="E37" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="F37" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="G37" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="H37" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="I37" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="J37" t="n">
-        <v>89.27944241175474</v>
+        <v>80.20157226632458</v>
       </c>
       <c r="K37" t="n">
-        <v>15.56522953080089</v>
+        <v>0.6475002703408634</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -30111,31 +30111,31 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>81.33004325169439</v>
+        <v>70.57830583243795</v>
       </c>
       <c r="R37" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="S37" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="T37" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="U37" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="V37" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="W37" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="X37" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="Y37" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
     </row>
     <row r="38">
@@ -30145,31 +30145,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="C38" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="D38" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="E38" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="F38" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="G38" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="H38" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="I38" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="J38" t="n">
-        <v>1.030857193808496</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -30193,28 +30193,28 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="S38" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="T38" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="U38" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="V38" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="W38" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="X38" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="Y38" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
     </row>
     <row r="39">
@@ -30224,28 +30224,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="C39" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="D39" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="E39" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="F39" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="G39" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="H39" t="n">
-        <v>111.5706895195153</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="I39" t="n">
-        <v>87.02682153066036</v>
+        <v>81.7537277694981</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30272,28 +30272,28 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>95.88432471868087</v>
+        <v>86.37529092466649</v>
       </c>
       <c r="S39" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="T39" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="U39" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="V39" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="W39" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="X39" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="Y39" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
     </row>
     <row r="40">
@@ -30303,34 +30303,34 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="C40" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="D40" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="E40" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="F40" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="G40" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="H40" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="I40" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="J40" t="n">
-        <v>89.27944241175474</v>
+        <v>80.20157226632458</v>
       </c>
       <c r="K40" t="n">
-        <v>15.56522953080089</v>
+        <v>0.6475002703408634</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -30348,31 +30348,31 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>81.33004325169439</v>
+        <v>70.57830583243795</v>
       </c>
       <c r="R40" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="S40" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="T40" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="U40" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="V40" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="W40" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="X40" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="Y40" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
     </row>
     <row r="41">
@@ -30382,31 +30382,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="C41" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="D41" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="E41" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="F41" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="G41" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="H41" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="I41" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="J41" t="n">
-        <v>1.030857193808496</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -30430,28 +30430,28 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="S41" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="T41" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="U41" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="V41" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="W41" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="X41" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="Y41" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
     </row>
     <row r="42">
@@ -30461,28 +30461,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="C42" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="D42" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="E42" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="F42" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="G42" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="H42" t="n">
-        <v>111.5706895195153</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="I42" t="n">
-        <v>87.02682153066036</v>
+        <v>81.7537277694981</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30509,28 +30509,28 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>95.88432471868087</v>
+        <v>86.37529092466649</v>
       </c>
       <c r="S42" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="T42" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="U42" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="V42" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="W42" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="X42" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="Y42" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
     </row>
     <row r="43">
@@ -30540,34 +30540,34 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="C43" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="D43" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="E43" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="F43" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="G43" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="H43" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="I43" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="J43" t="n">
-        <v>89.27944241175474</v>
+        <v>80.20157226632458</v>
       </c>
       <c r="K43" t="n">
-        <v>15.56522953080089</v>
+        <v>0.6475002703408634</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -30585,31 +30585,31 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>81.33004325169439</v>
+        <v>70.57830583243795</v>
       </c>
       <c r="R43" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="S43" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="T43" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="U43" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="V43" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="W43" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="X43" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
       <c r="Y43" t="n">
-        <v>112</v>
+        <v>110.0915363396326</v>
       </c>
     </row>
     <row r="44">
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1286432160804019</v>
+        <v>0.4148886796700437</v>
       </c>
       <c r="H11" t="n">
-        <v>1.317467336683416</v>
+        <v>4.248978690670836</v>
       </c>
       <c r="I11" t="n">
-        <v>4.9595175879397</v>
+        <v>15.99499582297937</v>
       </c>
       <c r="J11" t="n">
-        <v>10.91843216080402</v>
+        <v>35.2131580761454</v>
       </c>
       <c r="K11" t="n">
-        <v>16.36389949748744</v>
+        <v>52.77539588657837</v>
       </c>
       <c r="L11" t="n">
-        <v>20.30086432160804</v>
+        <v>65.47254531703048</v>
       </c>
       <c r="M11" t="n">
-        <v>22.58862311557789</v>
+        <v>72.85082187411261</v>
       </c>
       <c r="N11" t="n">
-        <v>22.95413065326633</v>
+        <v>74.02962433522514</v>
       </c>
       <c r="O11" t="n">
-        <v>21.67493467336683</v>
+        <v>69.90407502675613</v>
       </c>
       <c r="P11" t="n">
-        <v>18.49905527638191</v>
+        <v>59.66151074740192</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.89202010050251</v>
+        <v>44.80330990671846</v>
       </c>
       <c r="R11" t="n">
-        <v>8.080884422110554</v>
+        <v>26.06175102432341</v>
       </c>
       <c r="S11" t="n">
-        <v>2.931457286432162</v>
+        <v>9.45427578798113</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5631356783919597</v>
+        <v>1.816175195255617</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01029145728643215</v>
+        <v>0.03319109437360349</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,49 +31749,49 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.06883018867924529</v>
+        <v>0.2219850138442127</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6647547169811322</v>
+        <v>2.143907896863844</v>
       </c>
       <c r="I12" t="n">
-        <v>2.369811320754717</v>
+        <v>7.642905081916973</v>
       </c>
       <c r="J12" t="n">
-        <v>6.502943396226416</v>
+        <v>20.97271571586924</v>
       </c>
       <c r="K12" t="n">
-        <v>11.11456603773585</v>
+        <v>35.84571164343149</v>
       </c>
       <c r="L12" t="n">
-        <v>14.94490566037736</v>
+        <v>48.19898294016558</v>
       </c>
       <c r="M12" t="n">
-        <v>17.44</v>
+        <v>56.24593969201828</v>
       </c>
       <c r="N12" t="n">
-        <v>17.90158490566038</v>
+        <v>57.73460235064899</v>
       </c>
       <c r="O12" t="n">
-        <v>16.37645283018868</v>
+        <v>52.81588178073248</v>
       </c>
       <c r="P12" t="n">
-        <v>13.14354716981132</v>
+        <v>42.3894014594269</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.786113207547171</v>
+        <v>28.3361922935174</v>
       </c>
       <c r="R12" t="n">
-        <v>4.273509433962266</v>
+        <v>13.78254322797665</v>
       </c>
       <c r="S12" t="n">
-        <v>1.278490566037735</v>
+        <v>4.123274270308071</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2774339622641508</v>
+        <v>0.8947553847492605</v>
       </c>
       <c r="U12" t="n">
-        <v>0.004528301886792455</v>
+        <v>0.01460427722659295</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05770491803278688</v>
+        <v>0.1861047786470751</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5130491803278692</v>
+        <v>1.654640668334905</v>
       </c>
       <c r="I13" t="n">
-        <v>1.735344262295082</v>
+        <v>5.596678252404768</v>
       </c>
       <c r="J13" t="n">
-        <v>4.079737704918032</v>
+        <v>13.1576078503482</v>
       </c>
       <c r="K13" t="n">
-        <v>6.704262295081965</v>
+        <v>21.62199155554199</v>
       </c>
       <c r="L13" t="n">
-        <v>8.579147540983607</v>
+        <v>27.66870499994787</v>
       </c>
       <c r="M13" t="n">
-        <v>9.045508196721309</v>
+        <v>29.17276998374104</v>
       </c>
       <c r="N13" t="n">
-        <v>8.830426229508202</v>
+        <v>28.4791067178747</v>
       </c>
       <c r="O13" t="n">
-        <v>8.156327868852461</v>
+        <v>26.30506453095204</v>
       </c>
       <c r="P13" t="n">
-        <v>6.979147540983603</v>
+        <v>22.50852704655169</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.832</v>
+        <v>15.58373741925644</v>
       </c>
       <c r="R13" t="n">
-        <v>2.594622950819671</v>
+        <v>8.367947592622118</v>
       </c>
       <c r="S13" t="n">
-        <v>1.005639344262295</v>
+        <v>3.243298733331298</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2465573770491802</v>
+        <v>0.7951749633102295</v>
       </c>
       <c r="U13" t="n">
-        <v>0.003147540983606561</v>
+        <v>0.01015116974438592</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,49 +31907,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1286432160804019</v>
+        <v>0.4148886796700437</v>
       </c>
       <c r="H14" t="n">
-        <v>1.317467336683416</v>
+        <v>4.248978690670836</v>
       </c>
       <c r="I14" t="n">
-        <v>4.9595175879397</v>
+        <v>15.99499582297937</v>
       </c>
       <c r="J14" t="n">
-        <v>10.91843216080402</v>
+        <v>35.2131580761454</v>
       </c>
       <c r="K14" t="n">
-        <v>16.36389949748744</v>
+        <v>52.77539588657837</v>
       </c>
       <c r="L14" t="n">
-        <v>20.30086432160804</v>
+        <v>65.47254531703048</v>
       </c>
       <c r="M14" t="n">
-        <v>22.58862311557789</v>
+        <v>72.85082187411261</v>
       </c>
       <c r="N14" t="n">
-        <v>22.95413065326633</v>
+        <v>74.02962433522514</v>
       </c>
       <c r="O14" t="n">
-        <v>21.67493467336683</v>
+        <v>69.90407502675613</v>
       </c>
       <c r="P14" t="n">
-        <v>18.49905527638191</v>
+        <v>59.66151074740192</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.89202010050251</v>
+        <v>44.80330990671846</v>
       </c>
       <c r="R14" t="n">
-        <v>8.080884422110554</v>
+        <v>26.06175102432341</v>
       </c>
       <c r="S14" t="n">
-        <v>2.931457286432162</v>
+        <v>9.45427578798113</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5631356783919597</v>
+        <v>1.816175195255617</v>
       </c>
       <c r="U14" t="n">
-        <v>0.01029145728643215</v>
+        <v>0.03319109437360349</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,49 +31986,49 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.06883018867924529</v>
+        <v>0.2219850138442127</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6647547169811322</v>
+        <v>2.143907896863844</v>
       </c>
       <c r="I15" t="n">
-        <v>2.369811320754717</v>
+        <v>7.642905081916973</v>
       </c>
       <c r="J15" t="n">
-        <v>6.502943396226416</v>
+        <v>20.97271571586924</v>
       </c>
       <c r="K15" t="n">
-        <v>11.11456603773585</v>
+        <v>35.84571164343149</v>
       </c>
       <c r="L15" t="n">
-        <v>14.94490566037736</v>
+        <v>48.19898294016558</v>
       </c>
       <c r="M15" t="n">
-        <v>17.44</v>
+        <v>56.24593969201828</v>
       </c>
       <c r="N15" t="n">
-        <v>17.90158490566038</v>
+        <v>57.73460235064899</v>
       </c>
       <c r="O15" t="n">
-        <v>16.37645283018868</v>
+        <v>52.81588178073248</v>
       </c>
       <c r="P15" t="n">
-        <v>13.14354716981132</v>
+        <v>42.3894014594269</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.786113207547171</v>
+        <v>28.3361922935174</v>
       </c>
       <c r="R15" t="n">
-        <v>4.273509433962266</v>
+        <v>13.78254322797665</v>
       </c>
       <c r="S15" t="n">
-        <v>1.278490566037735</v>
+        <v>4.123274270308071</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2774339622641508</v>
+        <v>0.8947553847492605</v>
       </c>
       <c r="U15" t="n">
-        <v>0.004528301886792455</v>
+        <v>0.01460427722659295</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05770491803278688</v>
+        <v>0.1861047786470751</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5130491803278692</v>
+        <v>1.654640668334905</v>
       </c>
       <c r="I16" t="n">
-        <v>1.735344262295082</v>
+        <v>5.596678252404768</v>
       </c>
       <c r="J16" t="n">
-        <v>4.079737704918032</v>
+        <v>13.1576078503482</v>
       </c>
       <c r="K16" t="n">
-        <v>6.704262295081965</v>
+        <v>21.62199155554199</v>
       </c>
       <c r="L16" t="n">
-        <v>8.579147540983607</v>
+        <v>27.66870499994787</v>
       </c>
       <c r="M16" t="n">
-        <v>9.045508196721309</v>
+        <v>29.17276998374104</v>
       </c>
       <c r="N16" t="n">
-        <v>8.830426229508202</v>
+        <v>28.4791067178747</v>
       </c>
       <c r="O16" t="n">
-        <v>8.156327868852461</v>
+        <v>26.30506453095204</v>
       </c>
       <c r="P16" t="n">
-        <v>6.979147540983603</v>
+        <v>22.50852704655169</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.832</v>
+        <v>15.58373741925644</v>
       </c>
       <c r="R16" t="n">
-        <v>2.594622950819671</v>
+        <v>8.367947592622118</v>
       </c>
       <c r="S16" t="n">
-        <v>1.005639344262295</v>
+        <v>3.243298733331298</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2465573770491802</v>
+        <v>0.7951749633102295</v>
       </c>
       <c r="U16" t="n">
-        <v>0.003147540983606561</v>
+        <v>0.01015116974438592</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,49 +32144,49 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1286432160804019</v>
+        <v>0.4148886796700437</v>
       </c>
       <c r="H17" t="n">
-        <v>1.317467336683416</v>
+        <v>4.248978690670836</v>
       </c>
       <c r="I17" t="n">
-        <v>4.9595175879397</v>
+        <v>15.99499582297937</v>
       </c>
       <c r="J17" t="n">
-        <v>10.91843216080402</v>
+        <v>35.2131580761454</v>
       </c>
       <c r="K17" t="n">
-        <v>16.36389949748744</v>
+        <v>52.77539588657837</v>
       </c>
       <c r="L17" t="n">
-        <v>20.30086432160804</v>
+        <v>65.47254531703048</v>
       </c>
       <c r="M17" t="n">
-        <v>22.58862311557789</v>
+        <v>72.85082187411261</v>
       </c>
       <c r="N17" t="n">
-        <v>22.95413065326633</v>
+        <v>74.02962433522514</v>
       </c>
       <c r="O17" t="n">
-        <v>21.67493467336683</v>
+        <v>69.90407502675613</v>
       </c>
       <c r="P17" t="n">
-        <v>18.49905527638191</v>
+        <v>59.66151074740192</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.89202010050251</v>
+        <v>44.80330990671846</v>
       </c>
       <c r="R17" t="n">
-        <v>8.080884422110554</v>
+        <v>26.06175102432341</v>
       </c>
       <c r="S17" t="n">
-        <v>2.931457286432162</v>
+        <v>9.45427578798113</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5631356783919597</v>
+        <v>1.816175195255617</v>
       </c>
       <c r="U17" t="n">
-        <v>0.01029145728643215</v>
+        <v>0.03319109437360349</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,49 +32223,49 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.06883018867924529</v>
+        <v>0.2219850138442127</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6647547169811322</v>
+        <v>2.143907896863844</v>
       </c>
       <c r="I18" t="n">
-        <v>2.369811320754717</v>
+        <v>7.642905081916973</v>
       </c>
       <c r="J18" t="n">
-        <v>6.502943396226416</v>
+        <v>20.97271571586924</v>
       </c>
       <c r="K18" t="n">
-        <v>11.11456603773585</v>
+        <v>35.84571164343149</v>
       </c>
       <c r="L18" t="n">
-        <v>14.94490566037736</v>
+        <v>48.19898294016558</v>
       </c>
       <c r="M18" t="n">
-        <v>17.44</v>
+        <v>56.24593969201828</v>
       </c>
       <c r="N18" t="n">
-        <v>17.90158490566038</v>
+        <v>57.73460235064899</v>
       </c>
       <c r="O18" t="n">
-        <v>16.37645283018868</v>
+        <v>52.81588178073248</v>
       </c>
       <c r="P18" t="n">
-        <v>13.14354716981132</v>
+        <v>42.3894014594269</v>
       </c>
       <c r="Q18" t="n">
-        <v>8.786113207547171</v>
+        <v>28.3361922935174</v>
       </c>
       <c r="R18" t="n">
-        <v>4.273509433962266</v>
+        <v>13.78254322797665</v>
       </c>
       <c r="S18" t="n">
-        <v>1.278490566037735</v>
+        <v>4.123274270308071</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2774339622641508</v>
+        <v>0.8947553847492605</v>
       </c>
       <c r="U18" t="n">
-        <v>0.004528301886792455</v>
+        <v>0.01460427722659295</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05770491803278688</v>
+        <v>0.1861047786470751</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5130491803278692</v>
+        <v>1.654640668334905</v>
       </c>
       <c r="I19" t="n">
-        <v>1.735344262295082</v>
+        <v>5.596678252404768</v>
       </c>
       <c r="J19" t="n">
-        <v>4.079737704918032</v>
+        <v>13.1576078503482</v>
       </c>
       <c r="K19" t="n">
-        <v>6.704262295081965</v>
+        <v>21.62199155554199</v>
       </c>
       <c r="L19" t="n">
-        <v>8.579147540983607</v>
+        <v>27.66870499994787</v>
       </c>
       <c r="M19" t="n">
-        <v>9.045508196721309</v>
+        <v>29.17276998374104</v>
       </c>
       <c r="N19" t="n">
-        <v>8.830426229508202</v>
+        <v>28.4791067178747</v>
       </c>
       <c r="O19" t="n">
-        <v>8.156327868852461</v>
+        <v>26.30506453095204</v>
       </c>
       <c r="P19" t="n">
-        <v>6.979147540983603</v>
+        <v>22.50852704655169</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.832</v>
+        <v>15.58373741925644</v>
       </c>
       <c r="R19" t="n">
-        <v>2.594622950819671</v>
+        <v>8.367947592622118</v>
       </c>
       <c r="S19" t="n">
-        <v>1.005639344262295</v>
+        <v>3.243298733331298</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2465573770491802</v>
+        <v>0.7951749633102295</v>
       </c>
       <c r="U19" t="n">
-        <v>0.003147540983606561</v>
+        <v>0.01015116974438592</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1286432160804019</v>
+        <v>0.4148886796700437</v>
       </c>
       <c r="H20" t="n">
-        <v>1.317467336683416</v>
+        <v>4.248978690670836</v>
       </c>
       <c r="I20" t="n">
-        <v>4.9595175879397</v>
+        <v>15.99499582297937</v>
       </c>
       <c r="J20" t="n">
-        <v>10.91843216080402</v>
+        <v>35.2131580761454</v>
       </c>
       <c r="K20" t="n">
-        <v>16.36389949748744</v>
+        <v>52.77539588657837</v>
       </c>
       <c r="L20" t="n">
-        <v>20.30086432160804</v>
+        <v>65.47254531703048</v>
       </c>
       <c r="M20" t="n">
-        <v>22.58862311557789</v>
+        <v>72.85082187411261</v>
       </c>
       <c r="N20" t="n">
-        <v>22.95413065326633</v>
+        <v>74.02962433522514</v>
       </c>
       <c r="O20" t="n">
-        <v>21.67493467336683</v>
+        <v>69.90407502675613</v>
       </c>
       <c r="P20" t="n">
-        <v>18.49905527638191</v>
+        <v>59.66151074740192</v>
       </c>
       <c r="Q20" t="n">
-        <v>13.89202010050251</v>
+        <v>44.80330990671846</v>
       </c>
       <c r="R20" t="n">
-        <v>8.080884422110554</v>
+        <v>26.06175102432341</v>
       </c>
       <c r="S20" t="n">
-        <v>2.931457286432162</v>
+        <v>9.45427578798113</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5631356783919597</v>
+        <v>1.816175195255617</v>
       </c>
       <c r="U20" t="n">
-        <v>0.01029145728643215</v>
+        <v>0.03319109437360349</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,49 +32460,49 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.06883018867924529</v>
+        <v>0.2219850138442127</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6647547169811322</v>
+        <v>2.143907896863844</v>
       </c>
       <c r="I21" t="n">
-        <v>2.369811320754717</v>
+        <v>7.642905081916973</v>
       </c>
       <c r="J21" t="n">
-        <v>6.502943396226416</v>
+        <v>20.97271571586924</v>
       </c>
       <c r="K21" t="n">
-        <v>11.11456603773585</v>
+        <v>35.84571164343149</v>
       </c>
       <c r="L21" t="n">
-        <v>14.94490566037736</v>
+        <v>48.19898294016558</v>
       </c>
       <c r="M21" t="n">
-        <v>17.44</v>
+        <v>56.24593969201828</v>
       </c>
       <c r="N21" t="n">
-        <v>17.90158490566038</v>
+        <v>57.73460235064899</v>
       </c>
       <c r="O21" t="n">
-        <v>16.37645283018868</v>
+        <v>52.81588178073248</v>
       </c>
       <c r="P21" t="n">
-        <v>13.14354716981132</v>
+        <v>42.3894014594269</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.786113207547171</v>
+        <v>28.3361922935174</v>
       </c>
       <c r="R21" t="n">
-        <v>4.273509433962266</v>
+        <v>13.78254322797665</v>
       </c>
       <c r="S21" t="n">
-        <v>1.278490566037735</v>
+        <v>4.123274270308071</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2774339622641508</v>
+        <v>0.8947553847492605</v>
       </c>
       <c r="U21" t="n">
-        <v>0.004528301886792455</v>
+        <v>0.01460427722659295</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.05770491803278688</v>
+        <v>0.1861047786470751</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5130491803278692</v>
+        <v>1.654640668334905</v>
       </c>
       <c r="I22" t="n">
-        <v>1.735344262295082</v>
+        <v>5.596678252404768</v>
       </c>
       <c r="J22" t="n">
-        <v>4.079737704918032</v>
+        <v>13.1576078503482</v>
       </c>
       <c r="K22" t="n">
-        <v>6.704262295081965</v>
+        <v>21.62199155554199</v>
       </c>
       <c r="L22" t="n">
-        <v>8.579147540983607</v>
+        <v>27.66870499994787</v>
       </c>
       <c r="M22" t="n">
-        <v>9.045508196721309</v>
+        <v>29.17276998374104</v>
       </c>
       <c r="N22" t="n">
-        <v>8.830426229508202</v>
+        <v>28.4791067178747</v>
       </c>
       <c r="O22" t="n">
-        <v>8.156327868852461</v>
+        <v>26.30506453095204</v>
       </c>
       <c r="P22" t="n">
-        <v>6.979147540983603</v>
+        <v>22.50852704655169</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.832</v>
+        <v>15.58373741925644</v>
       </c>
       <c r="R22" t="n">
-        <v>2.594622950819671</v>
+        <v>8.367947592622118</v>
       </c>
       <c r="S22" t="n">
-        <v>1.005639344262295</v>
+        <v>3.243298733331298</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2465573770491802</v>
+        <v>0.7951749633102295</v>
       </c>
       <c r="U22" t="n">
-        <v>0.003147540983606561</v>
+        <v>0.01015116974438592</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,49 +32618,49 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1286432160804019</v>
+        <v>0.4148886796700437</v>
       </c>
       <c r="H23" t="n">
-        <v>1.317467336683416</v>
+        <v>4.248978690670836</v>
       </c>
       <c r="I23" t="n">
-        <v>4.9595175879397</v>
+        <v>15.99499582297937</v>
       </c>
       <c r="J23" t="n">
-        <v>10.91843216080402</v>
+        <v>35.2131580761454</v>
       </c>
       <c r="K23" t="n">
-        <v>16.36389949748744</v>
+        <v>52.77539588657837</v>
       </c>
       <c r="L23" t="n">
-        <v>20.30086432160804</v>
+        <v>65.47254531703048</v>
       </c>
       <c r="M23" t="n">
-        <v>22.58862311557789</v>
+        <v>72.85082187411261</v>
       </c>
       <c r="N23" t="n">
-        <v>22.95413065326633</v>
+        <v>74.02962433522514</v>
       </c>
       <c r="O23" t="n">
-        <v>21.67493467336683</v>
+        <v>69.90407502675613</v>
       </c>
       <c r="P23" t="n">
-        <v>18.49905527638191</v>
+        <v>59.66151074740192</v>
       </c>
       <c r="Q23" t="n">
-        <v>13.89202010050251</v>
+        <v>44.80330990671846</v>
       </c>
       <c r="R23" t="n">
-        <v>8.080884422110554</v>
+        <v>26.06175102432341</v>
       </c>
       <c r="S23" t="n">
-        <v>2.931457286432162</v>
+        <v>9.45427578798113</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5631356783919597</v>
+        <v>1.816175195255617</v>
       </c>
       <c r="U23" t="n">
-        <v>0.01029145728643215</v>
+        <v>0.03319109437360349</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,49 +32697,49 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.06883018867924529</v>
+        <v>0.2219850138442127</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6647547169811322</v>
+        <v>2.143907896863844</v>
       </c>
       <c r="I24" t="n">
-        <v>2.369811320754717</v>
+        <v>7.642905081916973</v>
       </c>
       <c r="J24" t="n">
-        <v>6.502943396226416</v>
+        <v>20.97271571586924</v>
       </c>
       <c r="K24" t="n">
-        <v>11.11456603773585</v>
+        <v>35.84571164343149</v>
       </c>
       <c r="L24" t="n">
-        <v>14.94490566037736</v>
+        <v>48.19898294016558</v>
       </c>
       <c r="M24" t="n">
-        <v>17.44</v>
+        <v>56.24593969201828</v>
       </c>
       <c r="N24" t="n">
-        <v>17.90158490566038</v>
+        <v>57.73460235064899</v>
       </c>
       <c r="O24" t="n">
-        <v>16.37645283018868</v>
+        <v>52.81588178073248</v>
       </c>
       <c r="P24" t="n">
-        <v>13.14354716981132</v>
+        <v>42.3894014594269</v>
       </c>
       <c r="Q24" t="n">
-        <v>8.786113207547171</v>
+        <v>28.3361922935174</v>
       </c>
       <c r="R24" t="n">
-        <v>4.273509433962266</v>
+        <v>13.78254322797665</v>
       </c>
       <c r="S24" t="n">
-        <v>1.278490566037735</v>
+        <v>4.123274270308071</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2774339622641508</v>
+        <v>0.8947553847492605</v>
       </c>
       <c r="U24" t="n">
-        <v>0.004528301886792455</v>
+        <v>0.01460427722659295</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.05770491803278688</v>
+        <v>0.1861047786470751</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5130491803278692</v>
+        <v>1.654640668334905</v>
       </c>
       <c r="I25" t="n">
-        <v>1.735344262295082</v>
+        <v>5.596678252404768</v>
       </c>
       <c r="J25" t="n">
-        <v>4.079737704918032</v>
+        <v>13.1576078503482</v>
       </c>
       <c r="K25" t="n">
-        <v>6.704262295081965</v>
+        <v>21.62199155554199</v>
       </c>
       <c r="L25" t="n">
-        <v>8.579147540983607</v>
+        <v>27.66870499994787</v>
       </c>
       <c r="M25" t="n">
-        <v>9.045508196721309</v>
+        <v>29.17276998374104</v>
       </c>
       <c r="N25" t="n">
-        <v>8.830426229508202</v>
+        <v>28.4791067178747</v>
       </c>
       <c r="O25" t="n">
-        <v>8.156327868852461</v>
+        <v>26.30506453095204</v>
       </c>
       <c r="P25" t="n">
-        <v>6.979147540983603</v>
+        <v>22.50852704655169</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.832</v>
+        <v>15.58373741925644</v>
       </c>
       <c r="R25" t="n">
-        <v>2.594622950819671</v>
+        <v>8.367947592622118</v>
       </c>
       <c r="S25" t="n">
-        <v>1.005639344262295</v>
+        <v>3.243298733331298</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2465573770491802</v>
+        <v>0.7951749633102295</v>
       </c>
       <c r="U25" t="n">
-        <v>0.003147540983606561</v>
+        <v>0.01015116974438592</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1286432160804019</v>
+        <v>0.4148886796700437</v>
       </c>
       <c r="H26" t="n">
-        <v>1.317467336683416</v>
+        <v>4.248978690670836</v>
       </c>
       <c r="I26" t="n">
-        <v>4.9595175879397</v>
+        <v>15.99499582297937</v>
       </c>
       <c r="J26" t="n">
-        <v>10.91843216080402</v>
+        <v>35.2131580761454</v>
       </c>
       <c r="K26" t="n">
-        <v>16.36389949748744</v>
+        <v>52.77539588657837</v>
       </c>
       <c r="L26" t="n">
-        <v>20.30086432160804</v>
+        <v>65.47254531703048</v>
       </c>
       <c r="M26" t="n">
-        <v>22.58862311557789</v>
+        <v>72.85082187411261</v>
       </c>
       <c r="N26" t="n">
-        <v>22.95413065326633</v>
+        <v>74.02962433522514</v>
       </c>
       <c r="O26" t="n">
-        <v>21.67493467336683</v>
+        <v>69.90407502675613</v>
       </c>
       <c r="P26" t="n">
-        <v>18.49905527638191</v>
+        <v>59.66151074740192</v>
       </c>
       <c r="Q26" t="n">
-        <v>13.89202010050251</v>
+        <v>44.80330990671846</v>
       </c>
       <c r="R26" t="n">
-        <v>8.080884422110554</v>
+        <v>26.06175102432341</v>
       </c>
       <c r="S26" t="n">
-        <v>2.931457286432162</v>
+        <v>9.45427578798113</v>
       </c>
       <c r="T26" t="n">
-        <v>0.5631356783919597</v>
+        <v>1.816175195255617</v>
       </c>
       <c r="U26" t="n">
-        <v>0.01029145728643215</v>
+        <v>0.03319109437360349</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,49 +32934,49 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.06883018867924529</v>
+        <v>0.2219850138442127</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6647547169811322</v>
+        <v>2.143907896863844</v>
       </c>
       <c r="I27" t="n">
-        <v>2.369811320754717</v>
+        <v>7.642905081916973</v>
       </c>
       <c r="J27" t="n">
-        <v>6.502943396226416</v>
+        <v>20.97271571586924</v>
       </c>
       <c r="K27" t="n">
-        <v>11.11456603773585</v>
+        <v>35.84571164343149</v>
       </c>
       <c r="L27" t="n">
-        <v>14.94490566037736</v>
+        <v>48.19898294016558</v>
       </c>
       <c r="M27" t="n">
-        <v>17.44</v>
+        <v>56.24593969201828</v>
       </c>
       <c r="N27" t="n">
-        <v>17.90158490566038</v>
+        <v>57.73460235064899</v>
       </c>
       <c r="O27" t="n">
-        <v>16.37645283018868</v>
+        <v>52.81588178073248</v>
       </c>
       <c r="P27" t="n">
-        <v>13.14354716981132</v>
+        <v>42.3894014594269</v>
       </c>
       <c r="Q27" t="n">
-        <v>8.786113207547171</v>
+        <v>28.3361922935174</v>
       </c>
       <c r="R27" t="n">
-        <v>4.273509433962266</v>
+        <v>13.78254322797665</v>
       </c>
       <c r="S27" t="n">
-        <v>1.278490566037735</v>
+        <v>4.123274270308071</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2774339622641508</v>
+        <v>0.8947553847492605</v>
       </c>
       <c r="U27" t="n">
-        <v>0.004528301886792455</v>
+        <v>0.01460427722659295</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.05770491803278688</v>
+        <v>0.1861047786470751</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5130491803278692</v>
+        <v>1.654640668334905</v>
       </c>
       <c r="I28" t="n">
-        <v>1.735344262295082</v>
+        <v>5.596678252404768</v>
       </c>
       <c r="J28" t="n">
-        <v>4.079737704918032</v>
+        <v>13.1576078503482</v>
       </c>
       <c r="K28" t="n">
-        <v>6.704262295081965</v>
+        <v>21.62199155554199</v>
       </c>
       <c r="L28" t="n">
-        <v>8.579147540983607</v>
+        <v>27.66870499994787</v>
       </c>
       <c r="M28" t="n">
-        <v>9.045508196721309</v>
+        <v>29.17276998374104</v>
       </c>
       <c r="N28" t="n">
-        <v>8.830426229508202</v>
+        <v>28.4791067178747</v>
       </c>
       <c r="O28" t="n">
-        <v>8.156327868852461</v>
+        <v>26.30506453095204</v>
       </c>
       <c r="P28" t="n">
-        <v>6.979147540983603</v>
+        <v>22.50852704655169</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.832</v>
+        <v>15.58373741925644</v>
       </c>
       <c r="R28" t="n">
-        <v>2.594622950819671</v>
+        <v>8.367947592622118</v>
       </c>
       <c r="S28" t="n">
-        <v>1.005639344262295</v>
+        <v>3.243298733331298</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2465573770491802</v>
+        <v>0.7951749633102295</v>
       </c>
       <c r="U28" t="n">
-        <v>0.003147540983606561</v>
+        <v>0.01015116974438592</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1286432160804019</v>
+        <v>0.4148886796700437</v>
       </c>
       <c r="H29" t="n">
-        <v>1.317467336683416</v>
+        <v>4.248978690670836</v>
       </c>
       <c r="I29" t="n">
-        <v>4.9595175879397</v>
+        <v>15.99499582297937</v>
       </c>
       <c r="J29" t="n">
-        <v>10.91843216080402</v>
+        <v>35.2131580761454</v>
       </c>
       <c r="K29" t="n">
-        <v>16.36389949748744</v>
+        <v>52.77539588657837</v>
       </c>
       <c r="L29" t="n">
-        <v>20.30086432160804</v>
+        <v>65.47254531703048</v>
       </c>
       <c r="M29" t="n">
-        <v>22.58862311557789</v>
+        <v>72.85082187411261</v>
       </c>
       <c r="N29" t="n">
-        <v>22.95413065326633</v>
+        <v>74.02962433522514</v>
       </c>
       <c r="O29" t="n">
-        <v>21.67493467336683</v>
+        <v>69.90407502675613</v>
       </c>
       <c r="P29" t="n">
-        <v>18.49905527638191</v>
+        <v>59.66151074740192</v>
       </c>
       <c r="Q29" t="n">
-        <v>13.89202010050251</v>
+        <v>44.80330990671846</v>
       </c>
       <c r="R29" t="n">
-        <v>8.080884422110554</v>
+        <v>26.06175102432341</v>
       </c>
       <c r="S29" t="n">
-        <v>2.931457286432162</v>
+        <v>9.45427578798113</v>
       </c>
       <c r="T29" t="n">
-        <v>0.5631356783919597</v>
+        <v>1.816175195255617</v>
       </c>
       <c r="U29" t="n">
-        <v>0.01029145728643215</v>
+        <v>0.03319109437360349</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,49 +33171,49 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.06883018867924529</v>
+        <v>0.2219850138442127</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6647547169811322</v>
+        <v>2.143907896863844</v>
       </c>
       <c r="I30" t="n">
-        <v>2.369811320754717</v>
+        <v>7.642905081916973</v>
       </c>
       <c r="J30" t="n">
-        <v>6.502943396226416</v>
+        <v>20.97271571586924</v>
       </c>
       <c r="K30" t="n">
-        <v>11.11456603773585</v>
+        <v>35.84571164343149</v>
       </c>
       <c r="L30" t="n">
-        <v>14.94490566037736</v>
+        <v>48.19898294016558</v>
       </c>
       <c r="M30" t="n">
-        <v>17.44</v>
+        <v>56.24593969201828</v>
       </c>
       <c r="N30" t="n">
-        <v>17.90158490566038</v>
+        <v>57.73460235064899</v>
       </c>
       <c r="O30" t="n">
-        <v>16.37645283018868</v>
+        <v>52.81588178073248</v>
       </c>
       <c r="P30" t="n">
-        <v>13.14354716981132</v>
+        <v>42.3894014594269</v>
       </c>
       <c r="Q30" t="n">
-        <v>8.786113207547171</v>
+        <v>28.3361922935174</v>
       </c>
       <c r="R30" t="n">
-        <v>4.273509433962266</v>
+        <v>13.78254322797665</v>
       </c>
       <c r="S30" t="n">
-        <v>1.278490566037735</v>
+        <v>4.123274270308071</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2774339622641508</v>
+        <v>0.8947553847492605</v>
       </c>
       <c r="U30" t="n">
-        <v>0.004528301886792455</v>
+        <v>0.01460427722659295</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.05770491803278688</v>
+        <v>0.1861047786470751</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5130491803278692</v>
+        <v>1.654640668334905</v>
       </c>
       <c r="I31" t="n">
-        <v>1.735344262295082</v>
+        <v>5.596678252404768</v>
       </c>
       <c r="J31" t="n">
-        <v>4.079737704918032</v>
+        <v>13.1576078503482</v>
       </c>
       <c r="K31" t="n">
-        <v>6.704262295081965</v>
+        <v>21.62199155554199</v>
       </c>
       <c r="L31" t="n">
-        <v>8.579147540983607</v>
+        <v>27.66870499994787</v>
       </c>
       <c r="M31" t="n">
-        <v>9.045508196721309</v>
+        <v>29.17276998374104</v>
       </c>
       <c r="N31" t="n">
-        <v>8.830426229508202</v>
+        <v>28.4791067178747</v>
       </c>
       <c r="O31" t="n">
-        <v>8.156327868852461</v>
+        <v>26.30506453095204</v>
       </c>
       <c r="P31" t="n">
-        <v>6.979147540983603</v>
+        <v>22.50852704655169</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.832</v>
+        <v>15.58373741925644</v>
       </c>
       <c r="R31" t="n">
-        <v>2.594622950819671</v>
+        <v>8.367947592622118</v>
       </c>
       <c r="S31" t="n">
-        <v>1.005639344262295</v>
+        <v>3.243298733331298</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2465573770491802</v>
+        <v>0.7951749633102295</v>
       </c>
       <c r="U31" t="n">
-        <v>0.003147540983606561</v>
+        <v>0.01015116974438592</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,49 +33329,49 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1286432160804019</v>
+        <v>0.4148886796700437</v>
       </c>
       <c r="H32" t="n">
-        <v>1.317467336683416</v>
+        <v>4.248978690670836</v>
       </c>
       <c r="I32" t="n">
-        <v>4.9595175879397</v>
+        <v>15.99499582297937</v>
       </c>
       <c r="J32" t="n">
-        <v>10.91843216080402</v>
+        <v>35.2131580761454</v>
       </c>
       <c r="K32" t="n">
-        <v>16.36389949748744</v>
+        <v>52.77539588657837</v>
       </c>
       <c r="L32" t="n">
-        <v>20.30086432160804</v>
+        <v>65.47254531703048</v>
       </c>
       <c r="M32" t="n">
-        <v>22.58862311557789</v>
+        <v>72.85082187411261</v>
       </c>
       <c r="N32" t="n">
-        <v>22.95413065326633</v>
+        <v>74.02962433522514</v>
       </c>
       <c r="O32" t="n">
-        <v>21.67493467336683</v>
+        <v>69.90407502675613</v>
       </c>
       <c r="P32" t="n">
-        <v>18.49905527638191</v>
+        <v>59.66151074740192</v>
       </c>
       <c r="Q32" t="n">
-        <v>13.89202010050251</v>
+        <v>44.80330990671846</v>
       </c>
       <c r="R32" t="n">
-        <v>8.080884422110554</v>
+        <v>26.06175102432341</v>
       </c>
       <c r="S32" t="n">
-        <v>2.931457286432162</v>
+        <v>9.45427578798113</v>
       </c>
       <c r="T32" t="n">
-        <v>0.5631356783919597</v>
+        <v>1.816175195255617</v>
       </c>
       <c r="U32" t="n">
-        <v>0.01029145728643215</v>
+        <v>0.03319109437360349</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,49 +33408,49 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.06883018867924529</v>
+        <v>0.2219850138442127</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6647547169811322</v>
+        <v>2.143907896863844</v>
       </c>
       <c r="I33" t="n">
-        <v>2.369811320754717</v>
+        <v>7.642905081916973</v>
       </c>
       <c r="J33" t="n">
-        <v>6.502943396226416</v>
+        <v>20.97271571586924</v>
       </c>
       <c r="K33" t="n">
-        <v>11.11456603773585</v>
+        <v>35.84571164343149</v>
       </c>
       <c r="L33" t="n">
-        <v>14.94490566037736</v>
+        <v>48.19898294016558</v>
       </c>
       <c r="M33" t="n">
-        <v>17.44</v>
+        <v>56.24593969201828</v>
       </c>
       <c r="N33" t="n">
-        <v>17.90158490566038</v>
+        <v>57.73460235064899</v>
       </c>
       <c r="O33" t="n">
-        <v>16.37645283018868</v>
+        <v>52.81588178073248</v>
       </c>
       <c r="P33" t="n">
-        <v>13.14354716981132</v>
+        <v>42.3894014594269</v>
       </c>
       <c r="Q33" t="n">
-        <v>8.786113207547171</v>
+        <v>28.3361922935174</v>
       </c>
       <c r="R33" t="n">
-        <v>4.273509433962266</v>
+        <v>13.78254322797665</v>
       </c>
       <c r="S33" t="n">
-        <v>1.278490566037735</v>
+        <v>4.123274270308071</v>
       </c>
       <c r="T33" t="n">
-        <v>0.2774339622641508</v>
+        <v>0.8947553847492605</v>
       </c>
       <c r="U33" t="n">
-        <v>0.004528301886792455</v>
+        <v>0.01460427722659295</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.05770491803278688</v>
+        <v>0.1861047786470751</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5130491803278692</v>
+        <v>1.654640668334905</v>
       </c>
       <c r="I34" t="n">
-        <v>1.735344262295082</v>
+        <v>5.596678252404768</v>
       </c>
       <c r="J34" t="n">
-        <v>4.079737704918032</v>
+        <v>13.1576078503482</v>
       </c>
       <c r="K34" t="n">
-        <v>6.704262295081965</v>
+        <v>21.62199155554199</v>
       </c>
       <c r="L34" t="n">
-        <v>8.579147540983607</v>
+        <v>27.66870499994787</v>
       </c>
       <c r="M34" t="n">
-        <v>9.045508196721309</v>
+        <v>29.17276998374104</v>
       </c>
       <c r="N34" t="n">
-        <v>8.830426229508202</v>
+        <v>28.4791067178747</v>
       </c>
       <c r="O34" t="n">
-        <v>8.156327868852461</v>
+        <v>26.30506453095204</v>
       </c>
       <c r="P34" t="n">
-        <v>6.979147540983603</v>
+        <v>22.50852704655169</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.832</v>
+        <v>15.58373741925644</v>
       </c>
       <c r="R34" t="n">
-        <v>2.594622950819671</v>
+        <v>8.367947592622118</v>
       </c>
       <c r="S34" t="n">
-        <v>1.005639344262295</v>
+        <v>3.243298733331298</v>
       </c>
       <c r="T34" t="n">
-        <v>0.2465573770491802</v>
+        <v>0.7951749633102295</v>
       </c>
       <c r="U34" t="n">
-        <v>0.003147540983606561</v>
+        <v>0.01015116974438592</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1286432160804019</v>
+        <v>0.4148886796700437</v>
       </c>
       <c r="H35" t="n">
-        <v>1.317467336683416</v>
+        <v>4.248978690670836</v>
       </c>
       <c r="I35" t="n">
-        <v>4.9595175879397</v>
+        <v>15.99499582297937</v>
       </c>
       <c r="J35" t="n">
-        <v>10.91843216080402</v>
+        <v>35.2131580761454</v>
       </c>
       <c r="K35" t="n">
-        <v>16.36389949748744</v>
+        <v>52.77539588657837</v>
       </c>
       <c r="L35" t="n">
-        <v>20.30086432160804</v>
+        <v>65.47254531703048</v>
       </c>
       <c r="M35" t="n">
-        <v>22.58862311557789</v>
+        <v>72.85082187411261</v>
       </c>
       <c r="N35" t="n">
-        <v>22.95413065326633</v>
+        <v>74.02962433522514</v>
       </c>
       <c r="O35" t="n">
-        <v>21.67493467336683</v>
+        <v>69.90407502675613</v>
       </c>
       <c r="P35" t="n">
-        <v>18.49905527638191</v>
+        <v>59.66151074740192</v>
       </c>
       <c r="Q35" t="n">
-        <v>13.89202010050251</v>
+        <v>44.80330990671846</v>
       </c>
       <c r="R35" t="n">
-        <v>8.080884422110554</v>
+        <v>26.06175102432341</v>
       </c>
       <c r="S35" t="n">
-        <v>2.931457286432162</v>
+        <v>9.45427578798113</v>
       </c>
       <c r="T35" t="n">
-        <v>0.5631356783919597</v>
+        <v>1.816175195255617</v>
       </c>
       <c r="U35" t="n">
-        <v>0.01029145728643215</v>
+        <v>0.03319109437360349</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,49 +33645,49 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.06883018867924529</v>
+        <v>0.2219850138442127</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6647547169811322</v>
+        <v>2.143907896863844</v>
       </c>
       <c r="I36" t="n">
-        <v>2.369811320754717</v>
+        <v>7.642905081916973</v>
       </c>
       <c r="J36" t="n">
-        <v>6.502943396226416</v>
+        <v>20.97271571586924</v>
       </c>
       <c r="K36" t="n">
-        <v>11.11456603773585</v>
+        <v>35.84571164343149</v>
       </c>
       <c r="L36" t="n">
-        <v>14.94490566037736</v>
+        <v>48.19898294016558</v>
       </c>
       <c r="M36" t="n">
-        <v>17.44</v>
+        <v>56.24593969201828</v>
       </c>
       <c r="N36" t="n">
-        <v>17.90158490566038</v>
+        <v>57.73460235064899</v>
       </c>
       <c r="O36" t="n">
-        <v>16.37645283018868</v>
+        <v>52.81588178073248</v>
       </c>
       <c r="P36" t="n">
-        <v>13.14354716981132</v>
+        <v>42.3894014594269</v>
       </c>
       <c r="Q36" t="n">
-        <v>8.786113207547171</v>
+        <v>28.3361922935174</v>
       </c>
       <c r="R36" t="n">
-        <v>4.273509433962266</v>
+        <v>13.78254322797665</v>
       </c>
       <c r="S36" t="n">
-        <v>1.278490566037735</v>
+        <v>4.123274270308071</v>
       </c>
       <c r="T36" t="n">
-        <v>0.2774339622641508</v>
+        <v>0.8947553847492605</v>
       </c>
       <c r="U36" t="n">
-        <v>0.004528301886792455</v>
+        <v>0.01460427722659295</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.05770491803278688</v>
+        <v>0.1861047786470751</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5130491803278692</v>
+        <v>1.654640668334905</v>
       </c>
       <c r="I37" t="n">
-        <v>1.735344262295082</v>
+        <v>5.596678252404768</v>
       </c>
       <c r="J37" t="n">
-        <v>4.079737704918032</v>
+        <v>13.1576078503482</v>
       </c>
       <c r="K37" t="n">
-        <v>6.704262295081965</v>
+        <v>21.62199155554199</v>
       </c>
       <c r="L37" t="n">
-        <v>8.579147540983607</v>
+        <v>27.66870499994787</v>
       </c>
       <c r="M37" t="n">
-        <v>9.045508196721309</v>
+        <v>29.17276998374104</v>
       </c>
       <c r="N37" t="n">
-        <v>8.830426229508202</v>
+        <v>28.4791067178747</v>
       </c>
       <c r="O37" t="n">
-        <v>8.156327868852461</v>
+        <v>26.30506453095204</v>
       </c>
       <c r="P37" t="n">
-        <v>6.979147540983603</v>
+        <v>22.50852704655169</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.832</v>
+        <v>15.58373741925644</v>
       </c>
       <c r="R37" t="n">
-        <v>2.594622950819671</v>
+        <v>8.367947592622118</v>
       </c>
       <c r="S37" t="n">
-        <v>1.005639344262295</v>
+        <v>3.243298733331298</v>
       </c>
       <c r="T37" t="n">
-        <v>0.2465573770491802</v>
+        <v>0.7951749633102295</v>
       </c>
       <c r="U37" t="n">
-        <v>0.003147540983606561</v>
+        <v>0.01015116974438592</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1286432160804019</v>
+        <v>0.4148886796700437</v>
       </c>
       <c r="H38" t="n">
-        <v>1.317467336683416</v>
+        <v>4.248978690670836</v>
       </c>
       <c r="I38" t="n">
-        <v>4.9595175879397</v>
+        <v>15.99499582297937</v>
       </c>
       <c r="J38" t="n">
-        <v>10.91843216080402</v>
+        <v>35.2131580761454</v>
       </c>
       <c r="K38" t="n">
-        <v>16.36389949748744</v>
+        <v>52.77539588657837</v>
       </c>
       <c r="L38" t="n">
-        <v>20.30086432160804</v>
+        <v>65.47254531703048</v>
       </c>
       <c r="M38" t="n">
-        <v>22.58862311557789</v>
+        <v>72.85082187411261</v>
       </c>
       <c r="N38" t="n">
-        <v>22.95413065326633</v>
+        <v>74.02962433522514</v>
       </c>
       <c r="O38" t="n">
-        <v>21.67493467336683</v>
+        <v>69.90407502675613</v>
       </c>
       <c r="P38" t="n">
-        <v>18.49905527638191</v>
+        <v>59.66151074740192</v>
       </c>
       <c r="Q38" t="n">
-        <v>13.89202010050251</v>
+        <v>44.80330990671846</v>
       </c>
       <c r="R38" t="n">
-        <v>8.080884422110554</v>
+        <v>26.06175102432341</v>
       </c>
       <c r="S38" t="n">
-        <v>2.931457286432162</v>
+        <v>9.45427578798113</v>
       </c>
       <c r="T38" t="n">
-        <v>0.5631356783919597</v>
+        <v>1.816175195255617</v>
       </c>
       <c r="U38" t="n">
-        <v>0.01029145728643215</v>
+        <v>0.03319109437360349</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,49 +33882,49 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.06883018867924529</v>
+        <v>0.2219850138442127</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6647547169811322</v>
+        <v>2.143907896863844</v>
       </c>
       <c r="I39" t="n">
-        <v>2.369811320754717</v>
+        <v>7.642905081916973</v>
       </c>
       <c r="J39" t="n">
-        <v>6.502943396226416</v>
+        <v>20.97271571586924</v>
       </c>
       <c r="K39" t="n">
-        <v>11.11456603773585</v>
+        <v>35.84571164343149</v>
       </c>
       <c r="L39" t="n">
-        <v>14.94490566037736</v>
+        <v>48.19898294016558</v>
       </c>
       <c r="M39" t="n">
-        <v>17.44</v>
+        <v>56.24593969201828</v>
       </c>
       <c r="N39" t="n">
-        <v>17.90158490566038</v>
+        <v>57.73460235064899</v>
       </c>
       <c r="O39" t="n">
-        <v>16.37645283018868</v>
+        <v>52.81588178073248</v>
       </c>
       <c r="P39" t="n">
-        <v>13.14354716981132</v>
+        <v>42.3894014594269</v>
       </c>
       <c r="Q39" t="n">
-        <v>8.786113207547171</v>
+        <v>28.3361922935174</v>
       </c>
       <c r="R39" t="n">
-        <v>4.273509433962266</v>
+        <v>13.78254322797665</v>
       </c>
       <c r="S39" t="n">
-        <v>1.278490566037735</v>
+        <v>4.123274270308071</v>
       </c>
       <c r="T39" t="n">
-        <v>0.2774339622641508</v>
+        <v>0.8947553847492605</v>
       </c>
       <c r="U39" t="n">
-        <v>0.004528301886792455</v>
+        <v>0.01460427722659295</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.05770491803278688</v>
+        <v>0.1861047786470751</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5130491803278692</v>
+        <v>1.654640668334905</v>
       </c>
       <c r="I40" t="n">
-        <v>1.735344262295082</v>
+        <v>5.596678252404768</v>
       </c>
       <c r="J40" t="n">
-        <v>4.079737704918032</v>
+        <v>13.1576078503482</v>
       </c>
       <c r="K40" t="n">
-        <v>6.704262295081965</v>
+        <v>21.62199155554199</v>
       </c>
       <c r="L40" t="n">
-        <v>8.579147540983607</v>
+        <v>27.66870499994787</v>
       </c>
       <c r="M40" t="n">
-        <v>9.045508196721309</v>
+        <v>29.17276998374104</v>
       </c>
       <c r="N40" t="n">
-        <v>8.830426229508202</v>
+        <v>28.4791067178747</v>
       </c>
       <c r="O40" t="n">
-        <v>8.156327868852461</v>
+        <v>26.30506453095204</v>
       </c>
       <c r="P40" t="n">
-        <v>6.979147540983603</v>
+        <v>22.50852704655169</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.832</v>
+        <v>15.58373741925644</v>
       </c>
       <c r="R40" t="n">
-        <v>2.594622950819671</v>
+        <v>8.367947592622118</v>
       </c>
       <c r="S40" t="n">
-        <v>1.005639344262295</v>
+        <v>3.243298733331298</v>
       </c>
       <c r="T40" t="n">
-        <v>0.2465573770491802</v>
+        <v>0.7951749633102295</v>
       </c>
       <c r="U40" t="n">
-        <v>0.003147540983606561</v>
+        <v>0.01015116974438592</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1286432160804019</v>
+        <v>0.4148886796700437</v>
       </c>
       <c r="H41" t="n">
-        <v>1.317467336683416</v>
+        <v>4.248978690670836</v>
       </c>
       <c r="I41" t="n">
-        <v>4.9595175879397</v>
+        <v>15.99499582297937</v>
       </c>
       <c r="J41" t="n">
-        <v>10.91843216080402</v>
+        <v>35.2131580761454</v>
       </c>
       <c r="K41" t="n">
-        <v>16.36389949748744</v>
+        <v>52.77539588657837</v>
       </c>
       <c r="L41" t="n">
-        <v>20.30086432160804</v>
+        <v>65.47254531703048</v>
       </c>
       <c r="M41" t="n">
-        <v>22.58862311557789</v>
+        <v>72.85082187411261</v>
       </c>
       <c r="N41" t="n">
-        <v>22.95413065326633</v>
+        <v>74.02962433522514</v>
       </c>
       <c r="O41" t="n">
-        <v>21.67493467336683</v>
+        <v>69.90407502675613</v>
       </c>
       <c r="P41" t="n">
-        <v>18.49905527638191</v>
+        <v>59.66151074740192</v>
       </c>
       <c r="Q41" t="n">
-        <v>13.89202010050251</v>
+        <v>44.80330990671846</v>
       </c>
       <c r="R41" t="n">
-        <v>8.080884422110554</v>
+        <v>26.06175102432341</v>
       </c>
       <c r="S41" t="n">
-        <v>2.931457286432162</v>
+        <v>9.45427578798113</v>
       </c>
       <c r="T41" t="n">
-        <v>0.5631356783919597</v>
+        <v>1.816175195255617</v>
       </c>
       <c r="U41" t="n">
-        <v>0.01029145728643215</v>
+        <v>0.03319109437360349</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,49 +34119,49 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.06883018867924529</v>
+        <v>0.2219850138442127</v>
       </c>
       <c r="H42" t="n">
-        <v>0.6647547169811322</v>
+        <v>2.143907896863844</v>
       </c>
       <c r="I42" t="n">
-        <v>2.369811320754717</v>
+        <v>7.642905081916973</v>
       </c>
       <c r="J42" t="n">
-        <v>6.502943396226416</v>
+        <v>20.97271571586924</v>
       </c>
       <c r="K42" t="n">
-        <v>11.11456603773585</v>
+        <v>35.84571164343149</v>
       </c>
       <c r="L42" t="n">
-        <v>14.94490566037736</v>
+        <v>48.19898294016558</v>
       </c>
       <c r="M42" t="n">
-        <v>17.44</v>
+        <v>56.24593969201828</v>
       </c>
       <c r="N42" t="n">
-        <v>17.90158490566038</v>
+        <v>57.73460235064899</v>
       </c>
       <c r="O42" t="n">
-        <v>16.37645283018868</v>
+        <v>52.81588178073248</v>
       </c>
       <c r="P42" t="n">
-        <v>13.14354716981132</v>
+        <v>42.3894014594269</v>
       </c>
       <c r="Q42" t="n">
-        <v>8.786113207547171</v>
+        <v>28.3361922935174</v>
       </c>
       <c r="R42" t="n">
-        <v>4.273509433962266</v>
+        <v>13.78254322797665</v>
       </c>
       <c r="S42" t="n">
-        <v>1.278490566037735</v>
+        <v>4.123274270308071</v>
       </c>
       <c r="T42" t="n">
-        <v>0.2774339622641508</v>
+        <v>0.8947553847492605</v>
       </c>
       <c r="U42" t="n">
-        <v>0.004528301886792455</v>
+        <v>0.01460427722659295</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.05770491803278688</v>
+        <v>0.1861047786470751</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5130491803278692</v>
+        <v>1.654640668334905</v>
       </c>
       <c r="I43" t="n">
-        <v>1.735344262295082</v>
+        <v>5.596678252404768</v>
       </c>
       <c r="J43" t="n">
-        <v>4.079737704918032</v>
+        <v>13.1576078503482</v>
       </c>
       <c r="K43" t="n">
-        <v>6.704262295081965</v>
+        <v>21.62199155554199</v>
       </c>
       <c r="L43" t="n">
-        <v>8.579147540983607</v>
+        <v>27.66870499994787</v>
       </c>
       <c r="M43" t="n">
-        <v>9.045508196721309</v>
+        <v>29.17276998374104</v>
       </c>
       <c r="N43" t="n">
-        <v>8.830426229508202</v>
+        <v>28.4791067178747</v>
       </c>
       <c r="O43" t="n">
-        <v>8.156327868852461</v>
+        <v>26.30506453095204</v>
       </c>
       <c r="P43" t="n">
-        <v>6.979147540983603</v>
+        <v>22.50852704655169</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.832</v>
+        <v>15.58373741925644</v>
       </c>
       <c r="R43" t="n">
-        <v>2.594622950819671</v>
+        <v>8.367947592622118</v>
       </c>
       <c r="S43" t="n">
-        <v>1.005639344262295</v>
+        <v>3.243298733331298</v>
       </c>
       <c r="T43" t="n">
-        <v>0.2465573770491802</v>
+        <v>0.7951749633102295</v>
       </c>
       <c r="U43" t="n">
-        <v>0.003147540983606561</v>
+        <v>0.01015116974438592</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1286432160804019</v>
+        <v>0.4148886796700437</v>
       </c>
       <c r="H44" t="n">
-        <v>1.317467336683416</v>
+        <v>4.248978690670836</v>
       </c>
       <c r="I44" t="n">
-        <v>4.9595175879397</v>
+        <v>15.99499582297937</v>
       </c>
       <c r="J44" t="n">
-        <v>10.91843216080402</v>
+        <v>35.2131580761454</v>
       </c>
       <c r="K44" t="n">
-        <v>16.36389949748744</v>
+        <v>52.77539588657837</v>
       </c>
       <c r="L44" t="n">
-        <v>20.30086432160804</v>
+        <v>65.47254531703048</v>
       </c>
       <c r="M44" t="n">
-        <v>22.58862311557789</v>
+        <v>72.85082187411261</v>
       </c>
       <c r="N44" t="n">
-        <v>22.95413065326633</v>
+        <v>74.02962433522514</v>
       </c>
       <c r="O44" t="n">
-        <v>21.67493467336683</v>
+        <v>69.90407502675613</v>
       </c>
       <c r="P44" t="n">
-        <v>18.49905527638191</v>
+        <v>59.66151074740192</v>
       </c>
       <c r="Q44" t="n">
-        <v>13.89202010050251</v>
+        <v>44.80330990671846</v>
       </c>
       <c r="R44" t="n">
-        <v>8.080884422110554</v>
+        <v>26.06175102432341</v>
       </c>
       <c r="S44" t="n">
-        <v>2.931457286432162</v>
+        <v>9.45427578798113</v>
       </c>
       <c r="T44" t="n">
-        <v>0.5631356783919597</v>
+        <v>1.816175195255617</v>
       </c>
       <c r="U44" t="n">
-        <v>0.01029145728643215</v>
+        <v>0.03319109437360349</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,49 +34356,49 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.06883018867924529</v>
+        <v>0.2219850138442127</v>
       </c>
       <c r="H45" t="n">
-        <v>0.6647547169811322</v>
+        <v>2.143907896863844</v>
       </c>
       <c r="I45" t="n">
-        <v>2.369811320754717</v>
+        <v>7.642905081916973</v>
       </c>
       <c r="J45" t="n">
-        <v>6.502943396226416</v>
+        <v>20.97271571586924</v>
       </c>
       <c r="K45" t="n">
-        <v>11.11456603773585</v>
+        <v>35.84571164343149</v>
       </c>
       <c r="L45" t="n">
-        <v>14.94490566037736</v>
+        <v>48.19898294016558</v>
       </c>
       <c r="M45" t="n">
-        <v>17.44</v>
+        <v>56.24593969201828</v>
       </c>
       <c r="N45" t="n">
-        <v>17.90158490566038</v>
+        <v>57.73460235064899</v>
       </c>
       <c r="O45" t="n">
-        <v>16.37645283018868</v>
+        <v>52.81588178073248</v>
       </c>
       <c r="P45" t="n">
-        <v>13.14354716981132</v>
+        <v>42.3894014594269</v>
       </c>
       <c r="Q45" t="n">
-        <v>8.786113207547171</v>
+        <v>28.3361922935174</v>
       </c>
       <c r="R45" t="n">
-        <v>4.273509433962266</v>
+        <v>13.78254322797665</v>
       </c>
       <c r="S45" t="n">
-        <v>1.278490566037735</v>
+        <v>4.123274270308071</v>
       </c>
       <c r="T45" t="n">
-        <v>0.2774339622641508</v>
+        <v>0.8947553847492605</v>
       </c>
       <c r="U45" t="n">
-        <v>0.004528301886792455</v>
+        <v>0.01460427722659295</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.05770491803278688</v>
+        <v>0.1861047786470751</v>
       </c>
       <c r="H46" t="n">
-        <v>0.5130491803278692</v>
+        <v>1.654640668334905</v>
       </c>
       <c r="I46" t="n">
-        <v>1.735344262295082</v>
+        <v>5.596678252404768</v>
       </c>
       <c r="J46" t="n">
-        <v>4.079737704918032</v>
+        <v>13.1576078503482</v>
       </c>
       <c r="K46" t="n">
-        <v>6.704262295081965</v>
+        <v>21.62199155554199</v>
       </c>
       <c r="L46" t="n">
-        <v>8.579147540983607</v>
+        <v>27.66870499994787</v>
       </c>
       <c r="M46" t="n">
-        <v>9.045508196721309</v>
+        <v>29.17276998374104</v>
       </c>
       <c r="N46" t="n">
-        <v>8.830426229508202</v>
+        <v>28.4791067178747</v>
       </c>
       <c r="O46" t="n">
-        <v>8.156327868852461</v>
+        <v>26.30506453095204</v>
       </c>
       <c r="P46" t="n">
-        <v>6.979147540983603</v>
+        <v>22.50852704655169</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.832</v>
+        <v>15.58373741925644</v>
       </c>
       <c r="R46" t="n">
-        <v>2.594622950819671</v>
+        <v>8.367947592622118</v>
       </c>
       <c r="S46" t="n">
-        <v>1.005639344262295</v>
+        <v>3.243298733331298</v>
       </c>
       <c r="T46" t="n">
-        <v>0.2465573770491802</v>
+        <v>0.7951749633102295</v>
       </c>
       <c r="U46" t="n">
-        <v>0.003147540983606561</v>
+        <v>0.01015116974438592</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -35322,7 +35322,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.06048503312195e-12</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
